--- a/src/data/brands.xlsx
+++ b/src/data/brands.xlsx
@@ -2,21 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DA3C60-DBFD-4C76-B597-3C963703F202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A324216D-D127-45B2-8394-C11D393C2197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="96" windowWidth="11808" windowHeight="11076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Brands" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,57 +39,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Brand Name</t>
   </si>
   <si>
-    <t>Slug</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Website</t>
-  </si>
-  <si>
-    <t>Logo Path</t>
-  </si>
-  <si>
-    <t>Meta Title</t>
-  </si>
-  <si>
-    <t>Meta Description</t>
-  </si>
-  <si>
-    <t>Eastman</t>
-  </si>
-  <si>
-    <t>JRS Drive</t>
-  </si>
-  <si>
-    <t>FoxCare</t>
-  </si>
-  <si>
-    <t>Tata</t>
+    <t xml:space="preserve"> Slug</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Featured</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SEO Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Meta Description</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>samsung</t>
+  </si>
+  <si>
+    <t>Explore the latest electronics, smartphones, and home appliances from Samsung.</t>
+  </si>
+  <si>
+    <t>Samsung Products - Official Store</t>
+  </si>
+  <si>
+    <t>Shop certified Samsung electronics, phones, and accessories with top warranties.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -86,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -94,40 +111,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Pandas" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -150,44 +146,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -214,14 +210,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -248,6 +262,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -259,238 +291,214 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
+      <c r="G2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/data/brands.xlsx
+++ b/src/data/brands.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A324216D-D127-45B2-8394-C11D393C2197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27125DD0-4DE6-402F-A182-73EA7268DA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="396" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-96" yWindow="792" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="189">
   <si>
     <t>Brand Name</t>
   </si>
@@ -62,19 +63,550 @@
     <t xml:space="preserve"> Meta Description</t>
   </si>
   <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>samsung</t>
-  </si>
-  <si>
-    <t>Explore the latest electronics, smartphones, and home appliances from Samsung.</t>
-  </si>
-  <si>
-    <t>Samsung Products - Official Store</t>
-  </si>
-  <si>
-    <t>Shop certified Samsung electronics, phones, and accessories with top warranties.</t>
+    <t>Eastman</t>
+  </si>
+  <si>
+    <t>JRS Drive</t>
+  </si>
+  <si>
+    <t>Tata Solar</t>
+  </si>
+  <si>
+    <t>Camron Pro</t>
+  </si>
+  <si>
+    <t>taparia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taparia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STANLEY </t>
+  </si>
+  <si>
+    <t>Carbiforce</t>
+  </si>
+  <si>
+    <t>Delta UPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">powertuff </t>
+  </si>
+  <si>
+    <t>OMXE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MultiTec  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metaldur  </t>
+  </si>
+  <si>
+    <t>MAC MASTER</t>
+  </si>
+  <si>
+    <t>KINEE SOLAR</t>
+  </si>
+  <si>
+    <t>Loom Solar</t>
+  </si>
+  <si>
+    <t>Adani Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KENBROOK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGCO </t>
+  </si>
+  <si>
+    <t>9JackTools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOSCH </t>
+  </si>
+  <si>
+    <t>Xcel</t>
+  </si>
+  <si>
+    <t>Luminous</t>
+  </si>
+  <si>
+    <t>UTL</t>
+  </si>
+  <si>
+    <t>Fujiyama</t>
+  </si>
+  <si>
+    <t>TORQUE MASTER</t>
+  </si>
+  <si>
+    <t>ukava</t>
+  </si>
+  <si>
+    <t>Shakti</t>
+  </si>
+  <si>
+    <t>Xtra Power</t>
+  </si>
+  <si>
+    <t>Slug</t>
+  </si>
+  <si>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>Featured</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SEO Title</t>
+  </si>
+  <si>
+    <t>Meta Description</t>
+  </si>
+  <si>
+    <t>eastman</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Explore Eastman power tools, hand tools, automotive tools, workshop equipment and industrial products available at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>Eastman Tools &amp; Equipment Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Eastman power tools, hand tools, workshop equipment and industrial tools with specifications and competitive pricing at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>jrs-drive</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Discover JRS Drive industrial tools, accessories and workshop products available through Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>JRS Drive Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find JRS Drive industrial tools, accessories and workshop products with specifications and buying guidance.</t>
+  </si>
+  <si>
+    <t>INGCO</t>
+  </si>
+  <si>
+    <t>ingco</t>
+  </si>
+  <si>
+    <t>Shop INGCO power tools, hand tools, garden tools, safety equipment and accessories at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>INGCO Tools Online India | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse INGCO power tools, hand tools, garden equipment and accessories with product details and specifications.</t>
+  </si>
+  <si>
+    <t>tata-solar</t>
+  </si>
+  <si>
+    <t>Explore Tata Solar panels, rooftop solar solutions and renewable energy products at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>Tata Solar Panels &amp; Solutions | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Discover Tata Solar panels, rooftop solar systems and solar solutions for residential and commercial applications.</t>
+  </si>
+  <si>
+    <t>camron-pro</t>
+  </si>
+  <si>
+    <t>Browse Camron Pro power tools, accessories and industrial equipment at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>Camron Pro Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Camron Pro power tools and workshop accessories with detailed specifications.</t>
+  </si>
+  <si>
+    <t>torque-master</t>
+  </si>
+  <si>
+    <t>Discover Torque Master hand tools, sockets, wrenches and workshop equipment.</t>
+  </si>
+  <si>
+    <t>Torque Master Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Torque Master hand tools, socket sets and workshop equipment online.</t>
+  </si>
+  <si>
+    <t>Taparia</t>
+  </si>
+  <si>
+    <t>Browse Taparia hand tools including screwdrivers, pliers, spanners, cutters and tool kits.</t>
+  </si>
+  <si>
+    <t>Taparia Hand Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Taparia hand tools with detailed specifications and competitive prices.</t>
+  </si>
+  <si>
+    <t>STANLEY</t>
+  </si>
+  <si>
+    <t>stanley</t>
+  </si>
+  <si>
+    <t>Explore Stanley professional hand tools, storage solutions, measuring tools and accessories.</t>
+  </si>
+  <si>
+    <t>Stanley Tools Online India | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Stanley hand tools, storage systems, measuring tools and workshop equipment.</t>
+  </si>
+  <si>
+    <t>carbiforce</t>
+  </si>
+  <si>
+    <t>Discover Carbiforce cutting tools, carbide accessories and industrial solutions.</t>
+  </si>
+  <si>
+    <t>Carbiforce Cutting Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Carbiforce carbide tools, cutting accessories and industrial products.</t>
+  </si>
+  <si>
+    <t>delta-ups</t>
+  </si>
+  <si>
+    <t>Explore Delta UPS systems, power backup solutions and electrical equipment.</t>
+  </si>
+  <si>
+    <t>Delta UPS Systems | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Delta UPS solutions, backup power systems and electrical equipment online.</t>
+  </si>
+  <si>
+    <t>Powertuff</t>
+  </si>
+  <si>
+    <t>powertuff</t>
+  </si>
+  <si>
+    <t>Browse Powertuff industrial equipment, power tools and accessories.</t>
+  </si>
+  <si>
+    <t>Powertuff Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Powertuff tools, workshop equipment and industrial accessories.</t>
+  </si>
+  <si>
+    <t>omxe</t>
+  </si>
+  <si>
+    <t>Discover OMXE industrial tools, workshop products and accessories at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>OMXE Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop OMXE industrial tools and workshop equipment with detailed product information.</t>
+  </si>
+  <si>
+    <t>MultiTec</t>
+  </si>
+  <si>
+    <t>multitec</t>
+  </si>
+  <si>
+    <t>Browse MultiTec industrial equipment, machinery accessories and workshop products.</t>
+  </si>
+  <si>
+    <t>MultiTec Industrial Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find MultiTec workshop tools and industrial equipment online.</t>
+  </si>
+  <si>
+    <t>Metaldur</t>
+  </si>
+  <si>
+    <t>metaldur</t>
+  </si>
+  <si>
+    <t>Explore Metaldur abrasives, cutting discs and industrial consumables.</t>
+  </si>
+  <si>
+    <t>Metaldur Abrasives | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Metaldur cutting discs, abrasives and industrial consumables.</t>
+  </si>
+  <si>
+    <t>mac-master</t>
+  </si>
+  <si>
+    <t>Discover MAC MASTER workshop equipment, power tools and accessories.</t>
+  </si>
+  <si>
+    <t>MAC MASTER Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop MAC MASTER industrial tools and workshop products online.</t>
+  </si>
+  <si>
+    <t>9jacktools</t>
+  </si>
+  <si>
+    <t>Browse 9JackTools hand tools, lifting equipment and workshop accessories.</t>
+  </si>
+  <si>
+    <t>9JackTools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore 9JackTools workshop tools and lifting equipment.</t>
+  </si>
+  <si>
+    <t>BOSCH</t>
+  </si>
+  <si>
+    <t>bosch</t>
+  </si>
+  <si>
+    <t>Explore Bosch power tools, measuring tools, accessories and professional equipment.</t>
+  </si>
+  <si>
+    <t>Bosch Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Bosch power tools, accessories and professional equipment with specifications.</t>
+  </si>
+  <si>
+    <t>xcel</t>
+  </si>
+  <si>
+    <t>Discover Xcel industrial products, tools and workshop accessories.</t>
+  </si>
+  <si>
+    <t>Xcel Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Xcel tools and industrial accessories online.</t>
+  </si>
+  <si>
+    <t>xtra-power</t>
+  </si>
+  <si>
+    <t>Browse Xtra Power power tools, demolition tools, woodworking tools and accessories.</t>
+  </si>
+  <si>
+    <t>Xtra Power Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Xtra Power power tools and accessories for professional and DIY applications.</t>
+  </si>
+  <si>
+    <t>KENBROOK</t>
+  </si>
+  <si>
+    <t>kenbrook</t>
+  </si>
+  <si>
+    <t>Discover Kenbrook tools, workshop equipment and industrial products.</t>
+  </si>
+  <si>
+    <t>Kenbrook Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Kenbrook industrial tools and workshop equipment online.</t>
+  </si>
+  <si>
+    <t>kinee-solar</t>
+  </si>
+  <si>
+    <t>Explore Kinee Solar panels, inverters and renewable energy solutions.</t>
+  </si>
+  <si>
+    <t>Kinee Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Kinee Solar products for residential and commercial solar installations.</t>
+  </si>
+  <si>
+    <t>loom-solar</t>
+  </si>
+  <si>
+    <t>Shop Loom Solar panels, lithium batteries, inverters and rooftop solar solutions.</t>
+  </si>
+  <si>
+    <t>Loom Solar Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Loom Solar panels, batteries and rooftop solar systems.</t>
+  </si>
+  <si>
+    <t>adani-solar</t>
+  </si>
+  <si>
+    <t>Discover Adani Solar photovoltaic modules and solar energy products.</t>
+  </si>
+  <si>
+    <t>Adani Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Adani Solar panels and renewable energy solutions online.</t>
+  </si>
+  <si>
+    <t>luminous</t>
+  </si>
+  <si>
+    <t>Explore Luminous inverters, batteries, UPS systems and solar products.</t>
+  </si>
+  <si>
+    <t>Luminous Inverters &amp; Solar | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Luminous inverters, batteries, UPS and solar solutions.</t>
+  </si>
+  <si>
+    <t>utl</t>
+  </si>
+  <si>
+    <t>Browse UTL solar inverters, batteries, UPS systems and rooftop solar products.</t>
+  </si>
+  <si>
+    <t>UTL Solar Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find UTL solar inverters, batteries and power backup solutions.</t>
+  </si>
+  <si>
+    <t>fujiyama</t>
+  </si>
+  <si>
+    <t>Explore Fujiyama power backup products, inverters, batteries and solar equipment.</t>
+  </si>
+  <si>
+    <t>Fujiyama Solar &amp; Inverters | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Fujiyama inverters, batteries and solar power solutions.</t>
+  </si>
+  <si>
+    <t>Ukava</t>
+  </si>
+  <si>
+    <t>Discover Ukava tools, accessories and industrial products available at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>Ukava Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Ukava industrial tools and accessories online.</t>
+  </si>
+  <si>
+    <t>shakti</t>
+  </si>
+  <si>
+    <t>Browse Shakti pumps, motors, agricultural equipment and related products.</t>
+  </si>
+  <si>
+    <t>Shakti Products Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Shakti pumps, motors and industrial products with specifications.</t>
+  </si>
+  <si>
+    <t>https://www.eastmanshop.com/cdn/shop/files/EASTMAN_LOGO_2_d03dc81a-227c-4cb6-a832-13cea09fe67b_1968x500.webp?v=1781506228</t>
+  </si>
+  <si>
+    <t>https://jrsdrive.com/wp-content/uploads/2023/09/new-l.jpg</t>
+  </si>
+  <si>
+    <t>https://www.ingco.com/dist/static/logo.60e47430.png</t>
+  </si>
+  <si>
+    <t>https://www.tatapowersolar.com/wp-content/themes/tpsolar/assets/images/tata-power-solar-logo.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/e97088_d0c8e8ddda36461cace1e6ccadfc8b7f~mv2.jpg/v1/fill/w_374,h_110,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Camron%20Logo_edited.jpg</t>
+  </si>
+  <si>
+    <t>https://www.torquemaster.in/images/logo.jpg</t>
+  </si>
+  <si>
+    <t>https://www.tapariatools.com/images/logo_demo.png</t>
+  </si>
+  <si>
+    <t>https://www.stanleytools.com/sites/g/files/xnuzat941/files/stanley%402x.png</t>
+  </si>
+  <si>
+    <t>https://carbiforce.com/_next/image?url=%2FCarbiforce%20-%20Logo%20White.png&amp;w=640&amp;q=75</t>
+  </si>
+  <si>
+    <t>https://deltaelectronicsindia.com/images/logo.svg</t>
+  </si>
+  <si>
+    <t>https://blr1.vultrobjects.com/images/trademark/6750521/imageshrine/b573bdf40fcdf3d2a780325f401d59c1.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn.moglix.com/p/wRFsFYPvSIT9Z-xxlarge.jpg</t>
+  </si>
+  <si>
+    <t>https://www.multitec.in/images/logo@2x.png</t>
+  </si>
+  <si>
+    <t>https://metaldur.in/assets/images/metaldur-white.png</t>
+  </si>
+  <si>
+    <t>https://images1.mcmaster.com/init/gfx/MastheadLogo.svg?ver=1783591692</t>
+  </si>
+  <si>
+    <t>https://5.imimg.com/data5/ANDROID/Default/2022/12/DB/NL/LN/159455181/product-jpeg-500x500.jpg</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/svg</t>
+  </si>
+  <si>
+    <t>https://xtrapowertools.com/site-img/logo/header-logo.png</t>
+  </si>
+  <si>
+    <t>https://kenbrooksolar.com/wp-content/uploads/Kenbrook-Solar-Registered-Logo.png</t>
+  </si>
+  <si>
+    <t>https://www.kinee.net/uploads/46681/logo1.png</t>
+  </si>
+  <si>
+    <t>https://www.loomsolar.com/cdn/shop/files/Loom_logo_f50a89a5-291b-4c15-9a87-303dc061554e_140x@2x.png?v=1752208604</t>
+  </si>
+  <si>
+    <t>https://www.adanisolar.com/-/media/project/adanisolar/common/logosolar.png</t>
+  </si>
+  <si>
+    <t>https://lumprodsta.blob.core.windows.net/prodcontainer/assets/icons/LuminousLogoBlue.webp</t>
+  </si>
+  <si>
+    <t>https://www.upsinverter.com/wp-content/uploads/2020/10/BANNER1.png</t>
+  </si>
+  <si>
+    <t>https://www.fujiyamautlsolar.com/wp-content/uploads/2026/07/fujinew-1536x487.png</t>
+  </si>
+  <si>
+    <t>https://shaktipumps.com/wp-content/uploads/2025/03/logo-shakti-pumps.webp</t>
   </si>
 </sst>
 </file>
@@ -452,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -483,19 +1015,811 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" t="s">
+        <v>153</v>
+      </c>
+      <c r="G27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E70A261-4425-4D8C-8079-AA7F5B537E30}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/brands.xlsx
+++ b/src/data/brands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27125DD0-4DE6-402F-A182-73EA7268DA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7CE2F9-949A-4109-AB5B-DE81B869C608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="792" windowWidth="11808" windowHeight="11076" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="72" windowWidth="11808" windowHeight="11076" activeTab="1" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="511">
   <si>
     <t>Brand Name</t>
   </si>
@@ -78,30 +78,15 @@
     <t>taparia</t>
   </si>
   <si>
-    <t xml:space="preserve">Taparia </t>
-  </si>
-  <si>
-    <t xml:space="preserve">STANLEY </t>
-  </si>
-  <si>
     <t>Carbiforce</t>
   </si>
   <si>
     <t>Delta UPS</t>
   </si>
   <si>
-    <t xml:space="preserve">powertuff </t>
-  </si>
-  <si>
     <t>OMXE</t>
   </si>
   <si>
-    <t xml:space="preserve">MultiTec  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metaldur  </t>
-  </si>
-  <si>
     <t>MAC MASTER</t>
   </si>
   <si>
@@ -114,18 +99,9 @@
     <t>Adani Solar</t>
   </si>
   <si>
-    <t xml:space="preserve">KENBROOK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGCO </t>
-  </si>
-  <si>
     <t>9JackTools</t>
   </si>
   <si>
-    <t xml:space="preserve">BOSCH </t>
-  </si>
-  <si>
     <t>Xcel</t>
   </si>
   <si>
@@ -300,9 +276,6 @@
     <t>Find Delta UPS solutions, backup power systems and electrical equipment online.</t>
   </si>
   <si>
-    <t>Powertuff</t>
-  </si>
-  <si>
     <t>powertuff</t>
   </si>
   <si>
@@ -507,9 +480,6 @@
     <t>Browse Fujiyama inverters, batteries and solar power solutions.</t>
   </si>
   <si>
-    <t>Ukava</t>
-  </si>
-  <si>
     <t>Discover Ukava tools, accessories and industrial products available at Haryana.Tools.</t>
   </si>
   <si>
@@ -607,13 +577,1009 @@
   </si>
   <si>
     <t>https://shaktipumps.com/wp-content/uploads/2025/03/logo-shakti-pumps.webp</t>
+  </si>
+  <si>
+    <t>Primary Category</t>
+  </si>
+  <si>
+    <t>Makita</t>
+  </si>
+  <si>
+    <t>DeWalt</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>Metabo</t>
+  </si>
+  <si>
+    <t>Festool</t>
+  </si>
+  <si>
+    <t>Fein</t>
+  </si>
+  <si>
+    <t>Dongcheng</t>
+  </si>
+  <si>
+    <t>Stihl</t>
+  </si>
+  <si>
+    <t>Vikram Solar</t>
+  </si>
+  <si>
+    <t>RenewSys</t>
+  </si>
+  <si>
+    <t>Goldi Solar</t>
+  </si>
+  <si>
+    <t>Premier Energies</t>
+  </si>
+  <si>
+    <t>Panasonic Solar</t>
+  </si>
+  <si>
+    <t>Meguiar's</t>
+  </si>
+  <si>
+    <t>Turtle Wax</t>
+  </si>
+  <si>
+    <t>Formula 1</t>
+  </si>
+  <si>
+    <t>Sonax</t>
+  </si>
+  <si>
+    <t>Mothers</t>
+  </si>
+  <si>
+    <t>Chemical Guys</t>
+  </si>
+  <si>
+    <t>WaveX</t>
+  </si>
+  <si>
+    <t>Atlas Copco</t>
+  </si>
+  <si>
+    <t>Freemans</t>
+  </si>
+  <si>
+    <t>(None)</t>
+  </si>
+  <si>
+    <t>formula-1</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/31q82B7aLKL.AC.jpg</t>
+  </si>
+  <si>
+    <t>Explore Formula 1 car care products, waxes, polishes, and automotive detailing accessories.</t>
+  </si>
+  <si>
+    <t>Formula 1 Car Care Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Formula 1 car care products, waxes, and automotive detailing solutions online.</t>
+  </si>
+  <si>
+    <t>3M Auto</t>
+  </si>
+  <si>
+    <t>3m-auto</t>
+  </si>
+  <si>
+    <t>https://www.3m.com/3M/en_US/p/d/b00038555/</t>
+  </si>
+  <si>
+    <t>Discover 3M automotive detailing products, paint protection films, and cleaning compounds.</t>
+  </si>
+  <si>
+    <t>3M Automotive Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse 3M car care products, detailing solutions, and surface protection items.</t>
+  </si>
+  <si>
+    <t>meguiars</t>
+  </si>
+  <si>
+    <t>https://www.meguiars.com/sites/default/files/styles/logo/public/meguiars-logo.png</t>
+  </si>
+  <si>
+    <t>Shop Meguiar's professional car care products, ceramic coatings, and interior cleaners.</t>
+  </si>
+  <si>
+    <t>Meguiar's Car Care | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Meguiar's high-performance car waxes, polishes, and detailing accessories.</t>
+  </si>
+  <si>
+    <t>turtle-wax</t>
+  </si>
+  <si>
+    <t>https://www.turtlewax.com/cdn/shop/files/TurtleWax_Logo_2020_Black_300x.png</t>
+  </si>
+  <si>
+    <t>Browse Turtle Wax car care items, scratch removers, washing shampoos, and protective coatings.</t>
+  </si>
+  <si>
+    <t>Turtle Wax Car Care | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Turtle Wax exterior and interior car care products with detailed specs.</t>
+  </si>
+  <si>
+    <t>makita</t>
+  </si>
+  <si>
+    <t>https://www.makita.co.in/themes/makita/assets/images/logo.png</t>
+  </si>
+  <si>
+    <t>Explore Makita professional cordless power tools, outdoor equipment and accessories.</t>
+  </si>
+  <si>
+    <t>Makita Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Makita high-performance cordless and electric power tools with specs.</t>
+  </si>
+  <si>
+    <t>dewalt</t>
+  </si>
+  <si>
+    <t>https://www.dewalt.com/globalassets/dewalt/logo.svg</t>
+  </si>
+  <si>
+    <t>Discover DeWalt heavy-duty power tools, construction equipment and jobsite accessories.</t>
+  </si>
+  <si>
+    <t>DeWalt Power Tools India | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse DeWalt industrial power tools, drills, and professional hardware.</t>
+  </si>
+  <si>
+    <t>Hilti</t>
+  </si>
+  <si>
+    <t>hilti</t>
+  </si>
+  <si>
+    <t>https://www.hilti.group/medias/hilti-logo.svg?context=bWFzdGVyfHJvb3R8MTU4NHxhcHBsaWNhdGlvbi9zdmd8aDg0L2g5My84ODgxMTQ1MzM1MzI2LnN2Z3xkNDExNTA3Y2M2YzgzMmFiYzI5MDcyNDcyYzRiNDFjMDliMTEzMmZkMTBiMWJmZjA0MWU5OWQ3MWE4YzgwMTNk</t>
+  </si>
+  <si>
+    <t>Shop Hilti construction tools, heavy-duty fastening systems, and anchors.</t>
+  </si>
+  <si>
+    <t>Hilti Construction Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Hilti professional construction equipment and anchoring systems.</t>
+  </si>
+  <si>
+    <t>HiKOKI</t>
+  </si>
+  <si>
+    <t>hikoki</t>
+  </si>
+  <si>
+    <t>https://www.hikoki-powertools.com/common/images/logo.svg</t>
+  </si>
+  <si>
+    <t>Explore HiKOKI (formerly Hitachi) industrial power tools and cutting machinery.</t>
+  </si>
+  <si>
+    <t>HiKOKI Power Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse HiKOKI professional power tools and workshop equipment online.</t>
+  </si>
+  <si>
+    <t>Black + Decker</t>
+  </si>
+  <si>
+    <t>black-decker</t>
+  </si>
+  <si>
+    <t>https://www.blackanddecker.com/globalassets/black-and-decker/logo.svg</t>
+  </si>
+  <si>
+    <t>Discover Black + Decker home power tools, DIY equipment, and cleaning gear.</t>
+  </si>
+  <si>
+    <t>Black + Decker Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Black + Decker DIY power tools and home improvement hardware.</t>
+  </si>
+  <si>
+    <t>JK Files &amp; Engineering</t>
+  </si>
+  <si>
+    <t>jk-files</t>
+  </si>
+  <si>
+    <t>https://www.jkfiles.com/assets/images/logo.png</t>
+  </si>
+  <si>
+    <t>Browse JK Files industrial files, hand tools, and cutting equipment.</t>
+  </si>
+  <si>
+    <t>JK Files Hand Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore JK Files industrial hand tools, rasps, and engineering products.</t>
+  </si>
+  <si>
+    <t>KPT Industries</t>
+  </si>
+  <si>
+    <t>kpt-industries</t>
+  </si>
+  <si>
+    <t>https://www.kpt.co.in/images/logo.png</t>
+  </si>
+  <si>
+    <t>Shop KPT electric power tools, industrial drills, and grinding machinery.</t>
+  </si>
+  <si>
+    <t>KPT Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Discover KPT industrial electric power tools and workshop accessories.</t>
+  </si>
+  <si>
+    <t>Endico</t>
+  </si>
+  <si>
+    <t>endico</t>
+  </si>
+  <si>
+    <t>https://www.endicotools.com/images/logo.png</t>
+  </si>
+  <si>
+    <t>Explore Endico woodworking routers, cutting tools, and portable power equipment.</t>
+  </si>
+  <si>
+    <t>Endico Power Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Endico woodworking and industrial cutting tools online.</t>
+  </si>
+  <si>
+    <t>Ralliwolf</t>
+  </si>
+  <si>
+    <t>ralliwolf</t>
+  </si>
+  <si>
+    <t>https://ralliwolf.com/wp-content/uploads/2021/03/logo.png</t>
+  </si>
+  <si>
+    <t>Discover Ralliwolf portable industrial electric power tools and specialized gear.</t>
+  </si>
+  <si>
+    <t>Ralliwolf Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Ralliwolf industrial drills, grinders, and heavy-duty workshop equipment.</t>
+  </si>
+  <si>
+    <t>Waaree Solar</t>
+  </si>
+  <si>
+    <t>waaree-solar</t>
+  </si>
+  <si>
+    <t>https://www.waaree.com/images/waaree-logo.png</t>
+  </si>
+  <si>
+    <t>Explore Waaree solar PV modules, rooftop solutions, and green energy products.</t>
+  </si>
+  <si>
+    <t>Waaree Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Waaree high-efficiency solar panels and renewable energy systems.</t>
+  </si>
+  <si>
+    <t>vikram-solar</t>
+  </si>
+  <si>
+    <t>https://www.vikramsolar.com/wp-content/uploads/2021/03/vikram-solar-logo.png</t>
+  </si>
+  <si>
+    <t>Shop Vikram Solar photovoltaic modules and utility-scale solar power solutions.</t>
+  </si>
+  <si>
+    <t>Vikram Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Vikram Solar modules and sustainable rooftop energy systems.</t>
+  </si>
+  <si>
+    <t>ReNew Power</t>
+  </si>
+  <si>
+    <t>renew-power</t>
+  </si>
+  <si>
+    <t>https://renew.com/wp-content/uploads/2023/04/renew-logo.svg</t>
+  </si>
+  <si>
+    <t>Discover ReNew solar energy solutions, clean power generation, and equipment.</t>
+  </si>
+  <si>
+    <t>ReNew Energy Solutions | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore ReNew solar installations and commercial energy systems.</t>
+  </si>
+  <si>
+    <t>panasonic-solar</t>
+  </si>
+  <si>
+    <t>https://www.panasonic.com/content/dam/global/common/panasonic-logo.svg</t>
+  </si>
+  <si>
+    <t>Browse Panasonic solar panels, HIT modules, and advanced energy storage.</t>
+  </si>
+  <si>
+    <t>Panasonic Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Panasonic high-efficiency solar modules and home energy products.</t>
+  </si>
+  <si>
+    <t>Exide Solar</t>
+  </si>
+  <si>
+    <t>exide-solar</t>
+  </si>
+  <si>
+    <t>https://www.exideindustries.com/images/exide-logo.png</t>
+  </si>
+  <si>
+    <t>Explore Exide solar batteries, home UPS, and renewable power systems.</t>
+  </si>
+  <si>
+    <t>Exide Solar Batteries | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Exide solar storage batteries, inverters, and power backups.</t>
+  </si>
+  <si>
+    <t>Amaron Solar</t>
+  </si>
+  <si>
+    <t>amaron-solar</t>
+  </si>
+  <si>
+    <t>https://www.amaron.in/images/amaron-logo.png</t>
+  </si>
+  <si>
+    <t>Discover Amaron tubular batteries for solar applications and power backup.</t>
+  </si>
+  <si>
+    <t>Amaron Solar Batteries | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Amaron durable solar inverter batteries and power solutions.</t>
+  </si>
+  <si>
+    <t>milwaukee</t>
+  </si>
+  <si>
+    <t>https://www.milwaukeetool.com/Content/Images/header-logo.svg</t>
+  </si>
+  <si>
+    <t>Explore Milwaukee heavy-duty cordless power tools, M18/M12 battery systems, and trade hand tools.</t>
+  </si>
+  <si>
+    <t>Milwaukee Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Milwaukee heavy-duty cordless power tools, accessories, and professional jobsite gear.</t>
+  </si>
+  <si>
+    <t>dongcheng</t>
+  </si>
+  <si>
+    <t>https://www.dongchengtool.com/upload/20220623/1655974070.png</t>
+  </si>
+  <si>
+    <t>Discover Dongcheng power tools, angle grinders, demolition hammers, and cordless machinery.</t>
+  </si>
+  <si>
+    <t>Dongcheng Power Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Dongcheng industrial power tools, rotary drills, and power equipment online.</t>
+  </si>
+  <si>
+    <t>DCA</t>
+  </si>
+  <si>
+    <t>dca</t>
+  </si>
+  <si>
+    <t>https://www.dcatools.com/images/logo.png</t>
+  </si>
+  <si>
+    <t>Browse DCA commercial power tools, bench grinders, marble cutters, and drill machines.</t>
+  </si>
+  <si>
+    <t>DCA Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore DCA commercial power tools, woodworking gear, and workshop equipment.</t>
+  </si>
+  <si>
+    <t>festool</t>
+  </si>
+  <si>
+    <t>https://www.festool.com/assets/images/festool-logo.svg</t>
+  </si>
+  <si>
+    <t>Explore Festool precision woodworking tools, dust extractors, circular saws, and sanders.</t>
+  </si>
+  <si>
+    <t>Festool Precision Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Festool professional woodworking power tools, sanders, and dust extraction systems.</t>
+  </si>
+  <si>
+    <t>Dremel</t>
+  </si>
+  <si>
+    <t>dremel</t>
+  </si>
+  <si>
+    <t>https://www.dremel.com/static/dremel-logo.svg</t>
+  </si>
+  <si>
+    <t>Discover Dremel rotary tools, multi-tools, precision cutting accessories, and crafting tools.</t>
+  </si>
+  <si>
+    <t>Dremel Rotary Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Dremel high-precision rotary tools, attachments, and engraving accessories.</t>
+  </si>
+  <si>
+    <t>Groz</t>
+  </si>
+  <si>
+    <t>groz</t>
+  </si>
+  <si>
+    <t>https://www.groz-tools.com/media/logo/stores/1/GROZ_Logo_Red_Black_1.png</t>
+  </si>
+  <si>
+    <t>Shop Groz precision engineering hand tools, lubrication equipment, LED work lights, and vices.</t>
+  </si>
+  <si>
+    <t>Groz Hand Tools &amp; Equipment | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Groz industrial hand tools, fluid handling equipment, and workshop accessories.</t>
+  </si>
+  <si>
+    <t>freemans</t>
+  </si>
+  <si>
+    <t>https://freemans.net/images/logo.png</t>
+  </si>
+  <si>
+    <t>Browse Freemans measuring tapes, spirit levels, hand tools, and layout measuring accessories.</t>
+  </si>
+  <si>
+    <t>Freemans Measuring Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Freemans measuring tapes, spirit levels, and precision hand tools.</t>
+  </si>
+  <si>
+    <t>CUMI</t>
+  </si>
+  <si>
+    <t>cumi</t>
+  </si>
+  <si>
+    <t>https://www.cumi-muri.com/images/cumi-logo.png</t>
+  </si>
+  <si>
+    <t>Discover CUMI abrasives, grinding wheels, cutting discs, and coated abrasive sheets.</t>
+  </si>
+  <si>
+    <t>CUMI Abrasives &amp; Cutting Discs | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop CUMI industrial grinding wheels, cutting discs, and abrasives at Haryana.Tools.</t>
+  </si>
+  <si>
+    <t>wavex</t>
+  </si>
+  <si>
+    <t>https://wavex.in/cdn/shop/files/logo_180x.png</t>
+  </si>
+  <si>
+    <t>Explore WaveX car care products, ceramic coatings, car wash shampoos, and detailing sprays.</t>
+  </si>
+  <si>
+    <t>WaveX Car Care Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse WaveX automotive detailing products, foam wash shampoos, and ceramic polishes.</t>
+  </si>
+  <si>
+    <t>sonax</t>
+  </si>
+  <si>
+    <t>https://www.sonax.com/fileadmin/templates/images/sonax-logo.svg</t>
+  </si>
+  <si>
+    <t>Shop Sonax premium German car detailing formulations, wheel cleaners, and waxes.</t>
+  </si>
+  <si>
+    <t>Sonax Car Care Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Discover Sonax professional car polishes, interior cleaners, and protective waxes.</t>
+  </si>
+  <si>
+    <t>chemical-guys</t>
+  </si>
+  <si>
+    <t>https://www.chemicalguys.com/on/demandware.static/Sites-CG-Site/-/default/dw8374828b/images/cg-logo.svg</t>
+  </si>
+  <si>
+    <t>Browse Chemical Guys car detailing soaps, microfiber towels, polishes, and car waxes.</t>
+  </si>
+  <si>
+    <t>Chemical Guys Car Care | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Chemical Guys car wash soaps, detailing kits, and interior cleaning supplies.</t>
+  </si>
+  <si>
+    <t>Waxpol</t>
+  </si>
+  <si>
+    <t>waxpol</t>
+  </si>
+  <si>
+    <t>https://www.waxpol.com/images/logo.png</t>
+  </si>
+  <si>
+    <t>Discover Waxpol auto care products, car polishes, radiator coolants, and maintenance fluids.</t>
+  </si>
+  <si>
+    <t>Waxpol Automotive Care | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Waxpol car care waxes, polishes, coolants, and auto maintenance products.</t>
+  </si>
+  <si>
+    <t>mothers</t>
+  </si>
+  <si>
+    <t>https://mothers.com/cdn/shop/files/mothers-logo_180x.png</t>
+  </si>
+  <si>
+    <t>Explore Mothers car polishes, mag &amp; aluminum polishes, and exterior detailing sprays.</t>
+  </si>
+  <si>
+    <t>Mothers Car Care Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Mothers automotive cleaning compounds, polishes, and interior car care items.</t>
+  </si>
+  <si>
+    <t>ShineXpro</t>
+  </si>
+  <si>
+    <t>shinexpro</t>
+  </si>
+  <si>
+    <t>https://shinexpro.in/cdn/shop/files/shinexpro_logo_180x.png</t>
+  </si>
+  <si>
+    <t>Browse ShineXpro microfiber towels, quick detailers, ceramic coat sprays, and wash mitts.</t>
+  </si>
+  <si>
+    <t>ShineXpro Car Detailing | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop ShineXpro car care accessories, microfiber drying towels, and detailing sprays.</t>
+  </si>
+  <si>
+    <t>goldi-solar</t>
+  </si>
+  <si>
+    <t>https://goldisolar.com/wp-content/uploads/2023/03/goldi-logo.png</t>
+  </si>
+  <si>
+    <t>Discover Goldi Solar photovoltaic modules, rooftop solar panels, and solar energy systems.</t>
+  </si>
+  <si>
+    <t>Goldi Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Goldi Solar high-efficiency PV panels and commercial solar installations.</t>
+  </si>
+  <si>
+    <t>premier-energies</t>
+  </si>
+  <si>
+    <t>https://premierenergies.com/images/logo.png</t>
+  </si>
+  <si>
+    <t>Explore Premier Energies solar cell modules, solar rooftop kits, and green energy products.</t>
+  </si>
+  <si>
+    <t>Premier Energies Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Premier Energies solar PV modules and rooftop energy solutions.</t>
+  </si>
+  <si>
+    <t>Microtek</t>
+  </si>
+  <si>
+    <t>microtek</t>
+  </si>
+  <si>
+    <t>https://www.microtekdirect.com/images/logo.png</t>
+  </si>
+  <si>
+    <t>Shop Microtek solar inverters, solar PCUs, tubular solar batteries, and voltage stabilizers.</t>
+  </si>
+  <si>
+    <t>Microtek Solar &amp; Inverters | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Microtek solar PCUs, rooftop inverters, and power backup solutions online.</t>
+  </si>
+  <si>
+    <t>Havells</t>
+  </si>
+  <si>
+    <t>havells</t>
+  </si>
+  <si>
+    <t>https://www.havells.com/images/havells-logo.svg</t>
+  </si>
+  <si>
+    <t>Browse Havells solar panels, grid-tied inverters, solar water heaters, and electrical gear.</t>
+  </si>
+  <si>
+    <t>Havells Solar &amp; Electrical | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Discover Havells rooftop solar panels, inverters, and clean energy products.</t>
+  </si>
+  <si>
+    <t>Servotech</t>
+  </si>
+  <si>
+    <t>servotech</t>
+  </si>
+  <si>
+    <t>https://servotech.in/wp-content/uploads/2022/01/servotech-logo.png</t>
+  </si>
+  <si>
+    <t>Discover Servotech solar inverters, solar PV panels, and green power backup equipment.</t>
+  </si>
+  <si>
+    <t>Servotech Solar Systems | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Servotech solar inverters, panels, and renewable energy products online.</t>
+  </si>
+  <si>
+    <t>Su-Kam</t>
+  </si>
+  <si>
+    <t>su-kam</t>
+  </si>
+  <si>
+    <t>https://www.su-kam.com/images/su-kam-logo.png</t>
+  </si>
+  <si>
+    <t>Explore Su-Kam solar power systems, solar PCUs, inverters, and battery storage solutions.</t>
+  </si>
+  <si>
+    <t>Su-Kam Solar &amp; Inverters | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Su-Kam solar PCUs, power backup inverters, and solar battery storage options.</t>
+  </si>
+  <si>
+    <t>Ryobi</t>
+  </si>
+  <si>
+    <t>ryobi</t>
+  </si>
+  <si>
+    <t>https://www.ryobitools.com/medias/ryobi-logo.svg</t>
+  </si>
+  <si>
+    <t>Discover Ryobi cordless power tools, outdoor equipment, DIY hardware, and battery systems.</t>
+  </si>
+  <si>
+    <t>Ryobi Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Ryobi innovative cordless power tools and home improvement equipment.</t>
+  </si>
+  <si>
+    <t>Krost</t>
+  </si>
+  <si>
+    <t>krost</t>
+  </si>
+  <si>
+    <t>https://krost.in/cdn/shop/files/krost-logo.png</t>
+  </si>
+  <si>
+    <t>Explore Krost industrial power tools, heat guns, blowers, and workshop accessories.</t>
+  </si>
+  <si>
+    <t>Krost Power Tools India | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Krost electric power tools, hand tools, and workshop machinery online.</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>fischer</t>
+  </si>
+  <si>
+    <t>https://www.fischer.de/fischer-en/-/media/fischer-group/fischer-logo.svg</t>
+  </si>
+  <si>
+    <t>Shop Fischer high-performance anchoring systems, concrete fixings, and construction fasteners.</t>
+  </si>
+  <si>
+    <t>Fischer Fixings &amp; Anchors | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Fischer construction fasteners, wall plugs, and heavy-duty fixing solutions.</t>
+  </si>
+  <si>
+    <t>fein</t>
+  </si>
+  <si>
+    <t>https://fein.com/assets/images/fein-logo.svg</t>
+  </si>
+  <si>
+    <t>Discover Fein professional metalworking tools, high-performance core drills, and multi-tools.</t>
+  </si>
+  <si>
+    <t>Fein Professional Power Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Fein metalworking power tools, specialized grinders, and precision cutters.</t>
+  </si>
+  <si>
+    <t>atlas-copco</t>
+  </si>
+  <si>
+    <t>https://www.atlascopco.com/content/dam/atlas-copco/global/logos/atlas-copco-logo.svg</t>
+  </si>
+  <si>
+    <t>Explore Atlas Copco industrial compressors, pneumatic tools, and construction equipment.</t>
+  </si>
+  <si>
+    <t>Atlas Copco Industrial Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Atlas Copco pneumatic tools, portable energy equipment, and compressors.</t>
+  </si>
+  <si>
+    <t>Saatvik Green Energy</t>
+  </si>
+  <si>
+    <t>saatvik-solar</t>
+  </si>
+  <si>
+    <t>https://saatvikgroup.com/wp-content/uploads/2023/07/saatvik-logo.png</t>
+  </si>
+  <si>
+    <t>Browse Saatvik high-efficiency monocrystalline solar PV modules and green energy panels.</t>
+  </si>
+  <si>
+    <t>Saatvik Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Discover Saatvik solar PV modules and rooftop renewable energy solutions.</t>
+  </si>
+  <si>
+    <t>renewsys</t>
+  </si>
+  <si>
+    <t>https://www.renewsysworld.com/images/renewsys-logo.png</t>
+  </si>
+  <si>
+    <t>Explore RenewSys solar PV modules, encapsulants, backsheets, and solar components.</t>
+  </si>
+  <si>
+    <t>RenewSys Solar Products | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop RenewSys solar panels, photovoltaic components, and energy solutions.</t>
+  </si>
+  <si>
+    <t>Patanjali Solar</t>
+  </si>
+  <si>
+    <t>patanjali-solar</t>
+  </si>
+  <si>
+    <t>https://www.patanjaliayurved.net/assets/images/patanjali-logo.png</t>
+  </si>
+  <si>
+    <t>Discover Patanjali solar panels, renewable energy products, and eco-friendly systems.</t>
+  </si>
+  <si>
+    <t>Patanjali Solar Panels | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Patanjali solar energy solutions and sustainable power products online.</t>
+  </si>
+  <si>
+    <t>SKIL</t>
+  </si>
+  <si>
+    <t>skil</t>
+  </si>
+  <si>
+    <t>https://www.skil.com/globalassets/skil/logo.svg</t>
+  </si>
+  <si>
+    <t>Discover SKIL cordless power tools, circular saws, sanders, and DIY workshop gear.</t>
+  </si>
+  <si>
+    <t>SKIL Power Tools Online | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop SKIL reliable power tools, saws, and home improvement equipment.</t>
+  </si>
+  <si>
+    <t>metabo</t>
+  </si>
+  <si>
+    <t>https://www.metabo.com/medias/metabo-logo.svg</t>
+  </si>
+  <si>
+    <t>Explore Metabo heavy-duty industrial angle grinders, cordless metalworking tools, and saws.</t>
+  </si>
+  <si>
+    <t>Metabo Industrial Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Browse Metabo professional power tools, abrasives, and metalworking equipment.</t>
+  </si>
+  <si>
+    <t>stihl</t>
+  </si>
+  <si>
+    <t>https://www.stihl.com/assets/images/stihl-logo.svg</t>
+  </si>
+  <si>
+    <t>Shop Stihl outdoor power equipment, chainsaws, brush cutters, and garden tools.</t>
+  </si>
+  <si>
+    <t>Stihl Outdoor Power Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Stihl petrol and cordless chainsaws, trimmers, and forestry equipment.</t>
+  </si>
+  <si>
+    <t>Echo</t>
+  </si>
+  <si>
+    <t>echo</t>
+  </si>
+  <si>
+    <t>https://www.echo-usa.com/globalassets/echo-logo.svg</t>
+  </si>
+  <si>
+    <t>Discover Echo professional outdoor power equipment, blowers, trimmers, and chainsaws.</t>
+  </si>
+  <si>
+    <t>Echo Outdoor Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Echo professional gardening equipment, blowers, and lawn care tools.</t>
+  </si>
+  <si>
+    <t>Eibenstock</t>
+  </si>
+  <si>
+    <t>eibenstock</t>
+  </si>
+  <si>
+    <t>https://www.eibenstock.com/fileadmin/templates/images/logo.svg</t>
+  </si>
+  <si>
+    <t>Browse Eibenstock specialist professional power tools, core drills, and concrete grinders.</t>
+  </si>
+  <si>
+    <t>Eibenstock Specialist Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Eibenstock core drilling machines, concrete polishers, and construction tools.</t>
+  </si>
+  <si>
+    <t>Starrett</t>
+  </si>
+  <si>
+    <t>starrett</t>
+  </si>
+  <si>
+    <t>https://www.starrett.com/globalassets/starrett-logo.svg</t>
+  </si>
+  <si>
+    <t>Explore Starrett precision measuring instruments, hole saws, hack saws, and layout tools.</t>
+  </si>
+  <si>
+    <t>Starrett Precision Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Find Starrett measuring instruments, precision hand tools, and industrial blades.</t>
+  </si>
+  <si>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>kennedy</t>
+  </si>
+  <si>
+    <t>https://www.kennedy-tools.co.uk/images/logo.svg</t>
+  </si>
+  <si>
+    <t>Discover Kennedy industrial hand tools, workshop storage solutions, and cutting equipment.</t>
+  </si>
+  <si>
+    <t>Kennedy Industrial Tools | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Shop Kennedy workshop hand tools, tool chests, and mechanical equipment online.</t>
+  </si>
+  <si>
+    <t>Solis Solar</t>
+  </si>
+  <si>
+    <t>solis-solar</t>
+  </si>
+  <si>
+    <t>https://www.ginlong.com/images/solis-logo.png</t>
+  </si>
+  <si>
+    <t>Browse Ginlong Solis grid-tied solar inverters, hybrid inverters, and PV monitoring systems.</t>
+  </si>
+  <si>
+    <t>Solis Solar Inverters | Haryana.Tools</t>
+  </si>
+  <si>
+    <t>Explore Solis solar inverters, residential and commercial renewable energy solutions.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -626,6 +1592,28 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -635,7 +1623,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -643,15 +1631,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -984,10 +2004,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8F2F70-D1BF-44E2-90B8-B0E4DAB2F558}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1009,643 +2029,8 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>171</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" t="s">
-        <v>178</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="H1" t="s">
         <v>179</v>
-      </c>
-      <c r="D18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" t="s">
-        <v>180</v>
-      </c>
-      <c r="D20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" t="s">
-        <v>124</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" t="s">
-        <v>182</v>
-      </c>
-      <c r="D22" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" t="s">
-        <v>183</v>
-      </c>
-      <c r="D23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" t="s">
-        <v>137</v>
-      </c>
-      <c r="G23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" t="s">
-        <v>141</v>
-      </c>
-      <c r="G24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" t="s">
-        <v>185</v>
-      </c>
-      <c r="D25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" t="s">
-        <v>144</v>
-      </c>
-      <c r="F25" t="s">
-        <v>145</v>
-      </c>
-      <c r="G25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" t="s">
-        <v>148</v>
-      </c>
-      <c r="F26" t="s">
-        <v>149</v>
-      </c>
-      <c r="G26" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" t="s">
-        <v>152</v>
-      </c>
-      <c r="F27" t="s">
-        <v>153</v>
-      </c>
-      <c r="G27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" t="s">
-        <v>157</v>
-      </c>
-      <c r="G28" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" t="s">
-        <v>159</v>
-      </c>
-      <c r="C29" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" t="s">
-        <v>160</v>
-      </c>
-      <c r="F29" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1656,173 +2041,2145 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E70A261-4425-4D8C-8079-AA7F5B537E30}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.21875" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" s="6" customFormat="1" ht="28.8">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="100.8">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="3" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="129.6">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="B6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="3" customFormat="1" ht="43.2">
+      <c r="A8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+    <row r="10" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+    <row r="11" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="B13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="3" customFormat="1" ht="43.2">
+      <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="B16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="3" customFormat="1" ht="43.2">
+      <c r="A19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A21" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="3" customFormat="1" ht="86.4">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+      <c r="B23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="3" customFormat="1" ht="43.2">
+      <c r="A28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="3" customFormat="1" ht="72">
+      <c r="A29" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+      <c r="B29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
+      <c r="E30" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A31" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="3" customFormat="1" ht="57.6">
+      <c r="A32" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="3" customFormat="1" ht="58.2" thickBot="1">
+      <c r="A33" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A35" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="187.8" thickBot="1">
+      <c r="A36" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A37" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A38" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A39" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="42" thickBot="1">
+      <c r="A40" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A41" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A42" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A43" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="72.599999999999994" thickBot="1">
+      <c r="A44" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A45" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A46" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A47" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="43.8" thickBot="1">
+      <c r="A48" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A49" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A50" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A51" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="83.4" thickBot="1">
+      <c r="A52" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A53" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A54" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A55" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A56" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A57" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A58" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="87" thickBot="1">
+      <c r="A59" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A60" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A61" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A62" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A63" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A64" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A65" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A66" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="72.599999999999994" thickBot="1">
+      <c r="A67" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A68" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A69" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A70" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A71" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A72" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="72.599999999999994" thickBot="1">
+      <c r="A73" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A74" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A75" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A76" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A77" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A78" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A79" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A80" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="58.2" thickBot="1">
+      <c r="A81" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A82" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A83" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="69.599999999999994" thickBot="1">
+      <c r="A84" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="3"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="3"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="3"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="3"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="3"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="3"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="3"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="3"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="3"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="2"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="3"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="3"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="3"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="3"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="3"/>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="3"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="3"/>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="3"/>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2"/>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="3"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="3"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="3"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="3"/>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="3"/>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="3"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="3"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="3"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="3"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="3"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="3"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="3"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="3"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="3"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="3"/>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="3"/>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="3"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{E44BEDA6-2D79-4677-8744-60ADF7C17E5A}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{DA1DC669-C49A-4C9B-BCFA-5C572AF12A7F}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{8DE281CE-B03A-4D8C-B243-A38398917470}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{0F5EFF59-5397-4B15-A68F-7E229731C6AF}"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://static.wixstatic.com/media/e97088_d0c8e8ddda36461cace1e6ccadfc8b7f~mv2.jpg/v1/fill/w_374,h_110,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Camron Logo_edited.jpg" xr:uid="{271E1ECA-016B-4501-83AD-7610A398EFE1}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{56D09FB7-F2E5-431C-A977-6884FC29A889}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{EF297E98-C6D9-46AA-A78B-84E3AB3DCA0A}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{C89771F0-F5A9-42F1-A8BF-B7E0D0D90109}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{6B345D54-65E2-47EA-BD18-89645569C753}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{CFC5E898-5A6C-4CE7-8FBE-5E593CA88D70}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{F832BC7C-E8E3-4FC2-A6DA-68DCFFE9A880}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{8B65D036-BDF0-4330-86D9-7BA2472035A8}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{6DB28E8A-5ED7-426F-8974-FF8D192DCD49}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{FF5EEB5E-F9B5-4343-B3E4-F8B1DA1D4B90}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{38576126-7773-46EB-ABAD-97725EF1D75A}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{1823EFF0-5AE7-47AD-B37A-CC8505C27457}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{604E9CEA-AD24-4251-8387-6E8B42A3B89E}"/>
+    <hyperlink ref="C20" r:id="rId18" xr:uid="{3D0EF484-132B-4B29-B696-F19E32E45BF6}"/>
+    <hyperlink ref="C21" r:id="rId19" xr:uid="{1D192599-64AE-499B-BBB3-78FADE93ACE1}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{1632554B-1E6A-4FFC-AC08-CC99D8C46B43}"/>
+    <hyperlink ref="C23" r:id="rId21" xr:uid="{A426DA0E-5ECC-428A-9E0F-79AFBDFDC0A1}"/>
+    <hyperlink ref="C24" r:id="rId22" xr:uid="{E131E37A-2710-41A9-8E09-385A48A22B6E}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{619AAEF6-A880-4FF2-A6A1-9AAED52AA7C3}"/>
+    <hyperlink ref="C26" r:id="rId24" xr:uid="{65B04FD4-E0D6-4862-8502-4BF8E1730BA5}"/>
+    <hyperlink ref="C27" r:id="rId25" xr:uid="{85DD1AA7-7AAF-433F-B7CD-6FC2603C7066}"/>
+    <hyperlink ref="C29" r:id="rId26" xr:uid="{023EBDAF-B529-4349-A162-0526693D85BA}"/>
+    <hyperlink ref="C30" r:id="rId27" display="https://www.google.com/search?q=https%3A%2F%2Fm.media-amazon.com%2Fimages%2FI%2F31q82B7aLKL._AC_.jpg" xr:uid="{1B9622F9-CCE1-4C61-81D3-0CE8C213D5CB}"/>
+    <hyperlink ref="C31" r:id="rId28" display="https://www.google.com/search?q=https://www.3m.com/3M/en_US/p/d/b00038555/" xr:uid="{7B93C535-153D-4A6F-951B-A847717D7D50}"/>
+    <hyperlink ref="C32" r:id="rId29" display="https://www.google.com/search?q=https://www.meguiars.com/sites/default/files/styles/logo/public/meguiars-logo.png" xr:uid="{1A59EE14-C00C-48F7-96B5-8F305DB4B3E1}"/>
+    <hyperlink ref="C33" r:id="rId30" display="https://www.google.com/search?q=https://www.turtlewax.com/cdn/shop/files/TurtleWax_Logo_2020_Black_300x.png" xr:uid="{D4FEAF10-90C6-4653-965F-6853D0345B4F}"/>
+    <hyperlink ref="C34" r:id="rId31" display="https://www.google.com/search?q=https://www.makita.co.in/themes/makita/assets/images/logo.png" xr:uid="{FD59263B-D5B7-4324-ABE9-61F1A708E098}"/>
+    <hyperlink ref="C35" r:id="rId32" display="https://www.google.com/search?q=https://www.dewalt.com/globalassets/dewalt/logo.svg" xr:uid="{ED96214F-39AC-4665-A16E-10F4F4574662}"/>
+    <hyperlink ref="C36" r:id="rId33" display="https://www.google.com/search?q=https://www.hilti.group/medias/hilti-logo.svg%3Fcontext%3DbWFzdGVyfHJvb3R8MTU4NHxhcHBsaWNhdGlvbi9zdmd8aDg0L2g5My84ODgxMTQ1MzM1MzI2LnN2Z3xkNDExNTA3Y2M2YzgzMmFiYzI5MDcyNDcyYzRiNDFjMDliMTEzMmZkMTBiMWJmZjA0MWU5OWQ3MWE4YzgwMTNk" xr:uid="{81FCC64A-2129-43BA-A2E9-5E0E2C31BCE1}"/>
+    <hyperlink ref="C37" r:id="rId34" display="https://www.google.com/search?q=https://www.hikoki-powertools.com/common/images/logo.svg" xr:uid="{3FED8A3E-A3DC-4AF0-A4DF-41015CC14851}"/>
+    <hyperlink ref="C38" r:id="rId35" display="https://www.google.com/search?q=https://www.blackanddecker.com/globalassets/black-and-decker/logo.svg" xr:uid="{6FEA8AD6-B684-452F-9B5A-82CE99631BDF}"/>
+    <hyperlink ref="C39" r:id="rId36" display="https://www.google.com/search?q=https://www.jkfiles.com/assets/images/logo.png" xr:uid="{3105DCB7-568C-4CD8-AB39-6C77A61BF366}"/>
+    <hyperlink ref="C40" r:id="rId37" display="https://www.google.com/search?q=https://www.kpt.co.in/images/logo.png" xr:uid="{992C7E83-28FF-4030-A442-2DB7D69AF948}"/>
+    <hyperlink ref="C41" r:id="rId38" display="https://www.google.com/search?q=https://www.endicotools.com/images/logo.png" xr:uid="{19A0873A-3277-4366-9C3A-56E12D1F0BFC}"/>
+    <hyperlink ref="C42" r:id="rId39" display="https://www.google.com/search?q=https://ralliwolf.com/wp-content/uploads/2021/03/logo.png" xr:uid="{2EE44E54-8333-41D2-A254-30D9547DB8FA}"/>
+    <hyperlink ref="C43" r:id="rId40" display="https://www.google.com/search?q=https://www.waaree.com/images/waaree-logo.png" xr:uid="{FE751C54-1352-4B8D-BBA6-D9FA9E8BA48C}"/>
+    <hyperlink ref="C44" r:id="rId41" display="https://www.google.com/search?q=https://www.vikramsolar.com/wp-content/uploads/2021/03/vikram-solar-logo.png" xr:uid="{EAEE8EF6-0D6E-4FFA-91EB-0AAAFC641B6B}"/>
+    <hyperlink ref="C45" r:id="rId42" display="https://www.google.com/search?q=https://renew.com/wp-content/uploads/2023/04/renew-logo.svg" xr:uid="{5FC1F1BB-76BF-450D-969B-122821ADBC16}"/>
+    <hyperlink ref="C46" r:id="rId43" display="https://www.google.com/search?q=https://www.panasonic.com/content/dam/global/common/panasonic-logo.svg" xr:uid="{833220CD-0511-4647-9205-168D677D07C1}"/>
+    <hyperlink ref="C47" r:id="rId44" display="https://www.google.com/search?q=https://www.exideindustries.com/images/exide-logo.png" xr:uid="{EA0AA9B6-3668-4C1A-B4E7-43041E9D4675}"/>
+    <hyperlink ref="C48" r:id="rId45" display="https://www.google.com/search?q=https://www.amaron.in/images/amaron-logo.png" xr:uid="{B3B21DCF-771C-4F83-BA0A-DACCDF1B4C19}"/>
+    <hyperlink ref="C49" r:id="rId46" display="https://www.google.com/search?q=https://www.milwaukeetool.com/Content/Images/header-logo.svg" xr:uid="{A7AC2AAD-F57A-4D3A-A56A-3688724693E4}"/>
+    <hyperlink ref="C50" r:id="rId47" display="https://www.google.com/search?q=https://www.dongchengtool.com/upload/20220623/1655974070.png" xr:uid="{9226EB91-2983-4045-9A02-760AD3078FBC}"/>
+    <hyperlink ref="C51" r:id="rId48" display="https://www.google.com/search?q=https://www.dcatools.com/images/logo.png" xr:uid="{578003DD-265C-4FDB-8913-38700183080C}"/>
+    <hyperlink ref="C52" r:id="rId49" display="https://www.google.com/search?q=https://www.festool.com/assets/images/festool-logo.svg" xr:uid="{F03877C9-1A9B-4916-BF06-E3C02352D75E}"/>
+    <hyperlink ref="C53" r:id="rId50" display="https://www.google.com/search?q=https://www.dremel.com/static/dremel-logo.svg" xr:uid="{742FAAE0-E5F2-4D49-AD98-9830774E7C95}"/>
+    <hyperlink ref="C54" r:id="rId51" display="https://www.google.com/search?q=https://www.groz-tools.com/media/logo/stores/1/GROZ_Logo_Red_Black_1.png" xr:uid="{BDF273B5-705F-47C7-B7B4-D8D471A87D54}"/>
+    <hyperlink ref="C55" r:id="rId52" display="https://www.google.com/search?q=https://freemans.net/images/logo.png" xr:uid="{C13CE459-6FA3-44F7-9DAE-49F7A4E5FF8C}"/>
+    <hyperlink ref="C56" r:id="rId53" display="https://www.google.com/search?q=https://www.cumi-muri.com/images/cumi-logo.png" xr:uid="{BD9B5573-D44D-4BFE-AC60-CC3384563BBC}"/>
+    <hyperlink ref="C57" r:id="rId54" display="https://www.google.com/search?q=https://wavex.in/cdn/shop/files/logo_180x.png" xr:uid="{2734B9DE-FBD0-41B4-ACDC-4609327BB0B7}"/>
+    <hyperlink ref="C58" r:id="rId55" display="https://www.google.com/search?q=https://www.sonax.com/fileadmin/templates/images/sonax-logo.svg" xr:uid="{9147FE49-877C-4A7C-9E93-05DE3204E174}"/>
+    <hyperlink ref="C59" r:id="rId56" display="https://www.google.com/search?q=https://www.chemicalguys.com/on/demandware.static/Sites-CG-Site/-/default/dw8374828b/images/cg-logo.svg" xr:uid="{B05AEC87-ED10-499A-B084-DC3C65C09849}"/>
+    <hyperlink ref="C60" r:id="rId57" display="https://www.google.com/search?q=https://www.waxpol.com/images/logo.png" xr:uid="{56B35AD3-DE05-4790-9B41-9B371C990DCD}"/>
+    <hyperlink ref="C61" r:id="rId58" display="https://www.google.com/search?q=https://mothers.com/cdn/shop/files/mothers-logo_180x.png" xr:uid="{53577D6D-4F6B-4338-BD61-DA33C698204F}"/>
+    <hyperlink ref="C62" r:id="rId59" display="https://www.google.com/search?q=https://shinexpro.in/cdn/shop/files/shinexpro_logo_180x.png" xr:uid="{28757B15-33B0-4729-BB5D-563094C1225E}"/>
+    <hyperlink ref="C63" r:id="rId60" display="https://www.google.com/search?q=https://goldisolar.com/wp-content/uploads/2023/03/goldi-logo.png" xr:uid="{BCCDE8EC-1ACF-41F7-B028-432DF5152680}"/>
+    <hyperlink ref="C64" r:id="rId61" display="https://www.google.com/search?q=https://premierenergies.com/images/logo.png" xr:uid="{BDA4C34A-ED22-4827-9266-AAC5031DAE10}"/>
+    <hyperlink ref="C65" r:id="rId62" display="https://www.google.com/search?q=https://www.microtekdirect.com/images/logo.png" xr:uid="{6E4CA772-E471-48F9-B061-0AD32DBFAC96}"/>
+    <hyperlink ref="C66" r:id="rId63" display="https://www.google.com/search?q=https://www.havells.com/images/havells-logo.svg" xr:uid="{DB289A11-B589-43BF-A4E5-244F9B90AC16}"/>
+    <hyperlink ref="C67" r:id="rId64" display="https://www.google.com/search?q=https://servotech.in/wp-content/uploads/2022/01/servotech-logo.png" xr:uid="{78EEE294-14E0-4CC0-9A35-E5DD894A3738}"/>
+    <hyperlink ref="C68" r:id="rId65" display="https://www.google.com/search?q=https://www.su-kam.com/images/su-kam-logo.png" xr:uid="{9A393C89-D3B7-4EF8-9286-1EAEEA533037}"/>
+    <hyperlink ref="C69" r:id="rId66" display="https://www.google.com/search?q=https://www.ryobitools.com/medias/ryobi-logo.svg" xr:uid="{490288EE-AF63-452A-B7D5-C02EBE10836C}"/>
+    <hyperlink ref="C70" r:id="rId67" display="https://www.google.com/search?q=https://krost.in/cdn/shop/files/krost-logo.png" xr:uid="{56A33686-72E9-4FD3-B083-5D349AAC4774}"/>
+    <hyperlink ref="C71" r:id="rId68" display="https://www.google.com/search?q=https://www.fischer.de/fischer-en/-/media/fischer-group/fischer-logo.svg" xr:uid="{8E85E127-6596-475F-B722-28842E6F0E4D}"/>
+    <hyperlink ref="C72" r:id="rId69" display="https://www.google.com/search?q=https://fein.com/assets/images/fein-logo.svg" xr:uid="{E7941CB9-EDBB-4738-8D58-5A34ED53E43F}"/>
+    <hyperlink ref="C73" r:id="rId70" display="https://www.google.com/search?q=https://www.atlascopco.com/content/dam/atlas-copco/global/logos/atlas-copco-logo.svg" xr:uid="{03519C7E-8974-4D7C-9857-56EB90F38CE1}"/>
+    <hyperlink ref="C74" r:id="rId71" display="https://www.google.com/search?q=https://saatvikgroup.com/wp-content/uploads/2023/07/saatvik-logo.png" xr:uid="{6A5F8658-3F8E-4D89-84D2-56C95686DB30}"/>
+    <hyperlink ref="C75" r:id="rId72" display="https://www.google.com/search?q=https://www.renewsysworld.com/images/renewsys-logo.png" xr:uid="{90B76089-4655-4C51-8CEB-C5405D5390C1}"/>
+    <hyperlink ref="C76" r:id="rId73" display="https://www.google.com/search?q=https://www.patanjaliayurved.net/assets/images/patanjali-logo.png" xr:uid="{1079E9E1-B1F0-473C-8259-7909C852705C}"/>
+    <hyperlink ref="C77" r:id="rId74" display="https://www.google.com/search?q=https://www.skil.com/globalassets/skil/logo.svg" xr:uid="{A6AD9A2B-CE09-4BC2-AF7D-9F680D431E7E}"/>
+    <hyperlink ref="C78" r:id="rId75" display="https://www.google.com/search?q=https://www.metabo.com/medias/metabo-logo.svg" xr:uid="{2C81986A-67DE-4F52-A451-974006CAD72E}"/>
+    <hyperlink ref="C79" r:id="rId76" display="https://www.google.com/search?q=https://www.stihl.com/assets/images/stihl-logo.svg" xr:uid="{FBEB5890-06C3-4DED-9311-FF8EBAE4A683}"/>
+    <hyperlink ref="C80" r:id="rId77" display="https://www.google.com/search?q=https://www.echo-usa.com/globalassets/echo-logo.svg" xr:uid="{90698BEC-606F-4459-8FEC-9D4F52945E6B}"/>
+    <hyperlink ref="C81" r:id="rId78" display="https://www.google.com/search?q=https://www.eibenstock.com/fileadmin/templates/images/logo.svg" xr:uid="{B2E0D824-D938-4BB4-AA39-DC963D9ADD8B}"/>
+    <hyperlink ref="C82" r:id="rId79" display="https://www.google.com/search?q=https://www.starrett.com/globalassets/starrett-logo.svg" xr:uid="{041C250D-CAB6-488F-B8CE-303F205D0EA3}"/>
+    <hyperlink ref="C83" r:id="rId80" display="https://www.google.com/search?q=https://www.kennedy-tools.co.uk/images/logo.svg" xr:uid="{9346F320-6852-4969-BB35-A2E6003D3609}"/>
+    <hyperlink ref="C84" r:id="rId81" display="https://www.google.com/search?q=https://www.ginlong.com/images/solis-logo.png" xr:uid="{4170BB3F-F8EC-49BB-BE39-383A04F9EFCE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/data/brands.xlsx
+++ b/src/data/brands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gala\Documents\code\jk3\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7CE2F9-949A-4109-AB5B-DE81B869C608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D5D67-64D4-403C-8535-06C73D15BA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="72" windowWidth="11808" windowHeight="11076" activeTab="1" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6540F3E8-6E2B-46EF-8B33-43A96A14636B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -549,9 +549,6 @@
     <t>https://5.imimg.com/data5/ANDROID/Default/2022/12/DB/NL/LN/159455181/product-jpeg-500x500.jpg</t>
   </si>
   <si>
-    <t>http://www.w3.org/2000/svg</t>
-  </si>
-  <si>
     <t>https://xtrapowertools.com/site-img/logo/header-logo.png</t>
   </si>
   <si>
@@ -654,9 +651,6 @@
     <t>formula-1</t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/31q82B7aLKL.AC.jpg</t>
-  </si>
-  <si>
     <t>Explore Formula 1 car care products, waxes, polishes, and automotive detailing accessories.</t>
   </si>
   <si>
@@ -672,9 +666,6 @@
     <t>3m-auto</t>
   </si>
   <si>
-    <t>https://www.3m.com/3M/en_US/p/d/b00038555/</t>
-  </si>
-  <si>
     <t>Discover 3M automotive detailing products, paint protection films, and cleaning compounds.</t>
   </si>
   <si>
@@ -687,9 +678,6 @@
     <t>meguiars</t>
   </si>
   <si>
-    <t>https://www.meguiars.com/sites/default/files/styles/logo/public/meguiars-logo.png</t>
-  </si>
-  <si>
     <t>Shop Meguiar's professional car care products, ceramic coatings, and interior cleaners.</t>
   </si>
   <si>
@@ -702,9 +690,6 @@
     <t>turtle-wax</t>
   </si>
   <si>
-    <t>https://www.turtlewax.com/cdn/shop/files/TurtleWax_Logo_2020_Black_300x.png</t>
-  </si>
-  <si>
     <t>Browse Turtle Wax car care items, scratch removers, washing shampoos, and protective coatings.</t>
   </si>
   <si>
@@ -717,9 +702,6 @@
     <t>makita</t>
   </si>
   <si>
-    <t>https://www.makita.co.in/themes/makita/assets/images/logo.png</t>
-  </si>
-  <si>
     <t>Explore Makita professional cordless power tools, outdoor equipment and accessories.</t>
   </si>
   <si>
@@ -732,9 +714,6 @@
     <t>dewalt</t>
   </si>
   <si>
-    <t>https://www.dewalt.com/globalassets/dewalt/logo.svg</t>
-  </si>
-  <si>
     <t>Discover DeWalt heavy-duty power tools, construction equipment and jobsite accessories.</t>
   </si>
   <si>
@@ -750,9 +729,6 @@
     <t>hilti</t>
   </si>
   <si>
-    <t>https://www.hilti.group/medias/hilti-logo.svg?context=bWFzdGVyfHJvb3R8MTU4NHxhcHBsaWNhdGlvbi9zdmd8aDg0L2g5My84ODgxMTQ1MzM1MzI2LnN2Z3xkNDExNTA3Y2M2YzgzMmFiYzI5MDcyNDcyYzRiNDFjMDliMTEzMmZkMTBiMWJmZjA0MWU5OWQ3MWE4YzgwMTNk</t>
-  </si>
-  <si>
     <t>Shop Hilti construction tools, heavy-duty fastening systems, and anchors.</t>
   </si>
   <si>
@@ -768,9 +744,6 @@
     <t>hikoki</t>
   </si>
   <si>
-    <t>https://www.hikoki-powertools.com/common/images/logo.svg</t>
-  </si>
-  <si>
     <t>Explore HiKOKI (formerly Hitachi) industrial power tools and cutting machinery.</t>
   </si>
   <si>
@@ -786,9 +759,6 @@
     <t>black-decker</t>
   </si>
   <si>
-    <t>https://www.blackanddecker.com/globalassets/black-and-decker/logo.svg</t>
-  </si>
-  <si>
     <t>Discover Black + Decker home power tools, DIY equipment, and cleaning gear.</t>
   </si>
   <si>
@@ -804,9 +774,6 @@
     <t>jk-files</t>
   </si>
   <si>
-    <t>https://www.jkfiles.com/assets/images/logo.png</t>
-  </si>
-  <si>
     <t>Browse JK Files industrial files, hand tools, and cutting equipment.</t>
   </si>
   <si>
@@ -822,9 +789,6 @@
     <t>kpt-industries</t>
   </si>
   <si>
-    <t>https://www.kpt.co.in/images/logo.png</t>
-  </si>
-  <si>
     <t>Shop KPT electric power tools, industrial drills, and grinding machinery.</t>
   </si>
   <si>
@@ -840,9 +804,6 @@
     <t>endico</t>
   </si>
   <si>
-    <t>https://www.endicotools.com/images/logo.png</t>
-  </si>
-  <si>
     <t>Explore Endico woodworking routers, cutting tools, and portable power equipment.</t>
   </si>
   <si>
@@ -858,9 +819,6 @@
     <t>ralliwolf</t>
   </si>
   <si>
-    <t>https://ralliwolf.com/wp-content/uploads/2021/03/logo.png</t>
-  </si>
-  <si>
     <t>Discover Ralliwolf portable industrial electric power tools and specialized gear.</t>
   </si>
   <si>
@@ -876,9 +834,6 @@
     <t>waaree-solar</t>
   </si>
   <si>
-    <t>https://www.waaree.com/images/waaree-logo.png</t>
-  </si>
-  <si>
     <t>Explore Waaree solar PV modules, rooftop solutions, and green energy products.</t>
   </si>
   <si>
@@ -891,9 +846,6 @@
     <t>vikram-solar</t>
   </si>
   <si>
-    <t>https://www.vikramsolar.com/wp-content/uploads/2021/03/vikram-solar-logo.png</t>
-  </si>
-  <si>
     <t>Shop Vikram Solar photovoltaic modules and utility-scale solar power solutions.</t>
   </si>
   <si>
@@ -909,9 +861,6 @@
     <t>renew-power</t>
   </si>
   <si>
-    <t>https://renew.com/wp-content/uploads/2023/04/renew-logo.svg</t>
-  </si>
-  <si>
     <t>Discover ReNew solar energy solutions, clean power generation, and equipment.</t>
   </si>
   <si>
@@ -924,9 +873,6 @@
     <t>panasonic-solar</t>
   </si>
   <si>
-    <t>https://www.panasonic.com/content/dam/global/common/panasonic-logo.svg</t>
-  </si>
-  <si>
     <t>Browse Panasonic solar panels, HIT modules, and advanced energy storage.</t>
   </si>
   <si>
@@ -942,9 +888,6 @@
     <t>exide-solar</t>
   </si>
   <si>
-    <t>https://www.exideindustries.com/images/exide-logo.png</t>
-  </si>
-  <si>
     <t>Explore Exide solar batteries, home UPS, and renewable power systems.</t>
   </si>
   <si>
@@ -960,9 +903,6 @@
     <t>amaron-solar</t>
   </si>
   <si>
-    <t>https://www.amaron.in/images/amaron-logo.png</t>
-  </si>
-  <si>
     <t>Discover Amaron tubular batteries for solar applications and power backup.</t>
   </si>
   <si>
@@ -975,9 +915,6 @@
     <t>milwaukee</t>
   </si>
   <si>
-    <t>https://www.milwaukeetool.com/Content/Images/header-logo.svg</t>
-  </si>
-  <si>
     <t>Explore Milwaukee heavy-duty cordless power tools, M18/M12 battery systems, and trade hand tools.</t>
   </si>
   <si>
@@ -990,9 +927,6 @@
     <t>dongcheng</t>
   </si>
   <si>
-    <t>https://www.dongchengtool.com/upload/20220623/1655974070.png</t>
-  </si>
-  <si>
     <t>Discover Dongcheng power tools, angle grinders, demolition hammers, and cordless machinery.</t>
   </si>
   <si>
@@ -1008,9 +942,6 @@
     <t>dca</t>
   </si>
   <si>
-    <t>https://www.dcatools.com/images/logo.png</t>
-  </si>
-  <si>
     <t>Browse DCA commercial power tools, bench grinders, marble cutters, and drill machines.</t>
   </si>
   <si>
@@ -1023,9 +954,6 @@
     <t>festool</t>
   </si>
   <si>
-    <t>https://www.festool.com/assets/images/festool-logo.svg</t>
-  </si>
-  <si>
     <t>Explore Festool precision woodworking tools, dust extractors, circular saws, and sanders.</t>
   </si>
   <si>
@@ -1041,9 +969,6 @@
     <t>dremel</t>
   </si>
   <si>
-    <t>https://www.dremel.com/static/dremel-logo.svg</t>
-  </si>
-  <si>
     <t>Discover Dremel rotary tools, multi-tools, precision cutting accessories, and crafting tools.</t>
   </si>
   <si>
@@ -1059,9 +984,6 @@
     <t>groz</t>
   </si>
   <si>
-    <t>https://www.groz-tools.com/media/logo/stores/1/GROZ_Logo_Red_Black_1.png</t>
-  </si>
-  <si>
     <t>Shop Groz precision engineering hand tools, lubrication equipment, LED work lights, and vices.</t>
   </si>
   <si>
@@ -1074,9 +996,6 @@
     <t>freemans</t>
   </si>
   <si>
-    <t>https://freemans.net/images/logo.png</t>
-  </si>
-  <si>
     <t>Browse Freemans measuring tapes, spirit levels, hand tools, and layout measuring accessories.</t>
   </si>
   <si>
@@ -1092,9 +1011,6 @@
     <t>cumi</t>
   </si>
   <si>
-    <t>https://www.cumi-muri.com/images/cumi-logo.png</t>
-  </si>
-  <si>
     <t>Discover CUMI abrasives, grinding wheels, cutting discs, and coated abrasive sheets.</t>
   </si>
   <si>
@@ -1107,9 +1023,6 @@
     <t>wavex</t>
   </si>
   <si>
-    <t>https://wavex.in/cdn/shop/files/logo_180x.png</t>
-  </si>
-  <si>
     <t>Explore WaveX car care products, ceramic coatings, car wash shampoos, and detailing sprays.</t>
   </si>
   <si>
@@ -1122,9 +1035,6 @@
     <t>sonax</t>
   </si>
   <si>
-    <t>https://www.sonax.com/fileadmin/templates/images/sonax-logo.svg</t>
-  </si>
-  <si>
     <t>Shop Sonax premium German car detailing formulations, wheel cleaners, and waxes.</t>
   </si>
   <si>
@@ -1137,9 +1047,6 @@
     <t>chemical-guys</t>
   </si>
   <si>
-    <t>https://www.chemicalguys.com/on/demandware.static/Sites-CG-Site/-/default/dw8374828b/images/cg-logo.svg</t>
-  </si>
-  <si>
     <t>Browse Chemical Guys car detailing soaps, microfiber towels, polishes, and car waxes.</t>
   </si>
   <si>
@@ -1155,9 +1062,6 @@
     <t>waxpol</t>
   </si>
   <si>
-    <t>https://www.waxpol.com/images/logo.png</t>
-  </si>
-  <si>
     <t>Discover Waxpol auto care products, car polishes, radiator coolants, and maintenance fluids.</t>
   </si>
   <si>
@@ -1170,9 +1074,6 @@
     <t>mothers</t>
   </si>
   <si>
-    <t>https://mothers.com/cdn/shop/files/mothers-logo_180x.png</t>
-  </si>
-  <si>
     <t>Explore Mothers car polishes, mag &amp; aluminum polishes, and exterior detailing sprays.</t>
   </si>
   <si>
@@ -1188,9 +1089,6 @@
     <t>shinexpro</t>
   </si>
   <si>
-    <t>https://shinexpro.in/cdn/shop/files/shinexpro_logo_180x.png</t>
-  </si>
-  <si>
     <t>Browse ShineXpro microfiber towels, quick detailers, ceramic coat sprays, and wash mitts.</t>
   </si>
   <si>
@@ -1203,9 +1101,6 @@
     <t>goldi-solar</t>
   </si>
   <si>
-    <t>https://goldisolar.com/wp-content/uploads/2023/03/goldi-logo.png</t>
-  </si>
-  <si>
     <t>Discover Goldi Solar photovoltaic modules, rooftop solar panels, and solar energy systems.</t>
   </si>
   <si>
@@ -1218,9 +1113,6 @@
     <t>premier-energies</t>
   </si>
   <si>
-    <t>https://premierenergies.com/images/logo.png</t>
-  </si>
-  <si>
     <t>Explore Premier Energies solar cell modules, solar rooftop kits, and green energy products.</t>
   </si>
   <si>
@@ -1236,9 +1128,6 @@
     <t>microtek</t>
   </si>
   <si>
-    <t>https://www.microtekdirect.com/images/logo.png</t>
-  </si>
-  <si>
     <t>Shop Microtek solar inverters, solar PCUs, tubular solar batteries, and voltage stabilizers.</t>
   </si>
   <si>
@@ -1254,9 +1143,6 @@
     <t>havells</t>
   </si>
   <si>
-    <t>https://www.havells.com/images/havells-logo.svg</t>
-  </si>
-  <si>
     <t>Browse Havells solar panels, grid-tied inverters, solar water heaters, and electrical gear.</t>
   </si>
   <si>
@@ -1272,9 +1158,6 @@
     <t>servotech</t>
   </si>
   <si>
-    <t>https://servotech.in/wp-content/uploads/2022/01/servotech-logo.png</t>
-  </si>
-  <si>
     <t>Discover Servotech solar inverters, solar PV panels, and green power backup equipment.</t>
   </si>
   <si>
@@ -1290,9 +1173,6 @@
     <t>su-kam</t>
   </si>
   <si>
-    <t>https://www.su-kam.com/images/su-kam-logo.png</t>
-  </si>
-  <si>
     <t>Explore Su-Kam solar power systems, solar PCUs, inverters, and battery storage solutions.</t>
   </si>
   <si>
@@ -1308,9 +1188,6 @@
     <t>ryobi</t>
   </si>
   <si>
-    <t>https://www.ryobitools.com/medias/ryobi-logo.svg</t>
-  </si>
-  <si>
     <t>Discover Ryobi cordless power tools, outdoor equipment, DIY hardware, and battery systems.</t>
   </si>
   <si>
@@ -1326,9 +1203,6 @@
     <t>krost</t>
   </si>
   <si>
-    <t>https://krost.in/cdn/shop/files/krost-logo.png</t>
-  </si>
-  <si>
     <t>Explore Krost industrial power tools, heat guns, blowers, and workshop accessories.</t>
   </si>
   <si>
@@ -1344,9 +1218,6 @@
     <t>fischer</t>
   </si>
   <si>
-    <t>https://www.fischer.de/fischer-en/-/media/fischer-group/fischer-logo.svg</t>
-  </si>
-  <si>
     <t>Shop Fischer high-performance anchoring systems, concrete fixings, and construction fasteners.</t>
   </si>
   <si>
@@ -1359,9 +1230,6 @@
     <t>fein</t>
   </si>
   <si>
-    <t>https://fein.com/assets/images/fein-logo.svg</t>
-  </si>
-  <si>
     <t>Discover Fein professional metalworking tools, high-performance core drills, and multi-tools.</t>
   </si>
   <si>
@@ -1374,9 +1242,6 @@
     <t>atlas-copco</t>
   </si>
   <si>
-    <t>https://www.atlascopco.com/content/dam/atlas-copco/global/logos/atlas-copco-logo.svg</t>
-  </si>
-  <si>
     <t>Explore Atlas Copco industrial compressors, pneumatic tools, and construction equipment.</t>
   </si>
   <si>
@@ -1392,9 +1257,6 @@
     <t>saatvik-solar</t>
   </si>
   <si>
-    <t>https://saatvikgroup.com/wp-content/uploads/2023/07/saatvik-logo.png</t>
-  </si>
-  <si>
     <t>Browse Saatvik high-efficiency monocrystalline solar PV modules and green energy panels.</t>
   </si>
   <si>
@@ -1407,9 +1269,6 @@
     <t>renewsys</t>
   </si>
   <si>
-    <t>https://www.renewsysworld.com/images/renewsys-logo.png</t>
-  </si>
-  <si>
     <t>Explore RenewSys solar PV modules, encapsulants, backsheets, and solar components.</t>
   </si>
   <si>
@@ -1425,9 +1284,6 @@
     <t>patanjali-solar</t>
   </si>
   <si>
-    <t>https://www.patanjaliayurved.net/assets/images/patanjali-logo.png</t>
-  </si>
-  <si>
     <t>Discover Patanjali solar panels, renewable energy products, and eco-friendly systems.</t>
   </si>
   <si>
@@ -1443,9 +1299,6 @@
     <t>skil</t>
   </si>
   <si>
-    <t>https://www.skil.com/globalassets/skil/logo.svg</t>
-  </si>
-  <si>
     <t>Discover SKIL cordless power tools, circular saws, sanders, and DIY workshop gear.</t>
   </si>
   <si>
@@ -1458,9 +1311,6 @@
     <t>metabo</t>
   </si>
   <si>
-    <t>https://www.metabo.com/medias/metabo-logo.svg</t>
-  </si>
-  <si>
     <t>Explore Metabo heavy-duty industrial angle grinders, cordless metalworking tools, and saws.</t>
   </si>
   <si>
@@ -1473,9 +1323,6 @@
     <t>stihl</t>
   </si>
   <si>
-    <t>https://www.stihl.com/assets/images/stihl-logo.svg</t>
-  </si>
-  <si>
     <t>Shop Stihl outdoor power equipment, chainsaws, brush cutters, and garden tools.</t>
   </si>
   <si>
@@ -1491,9 +1338,6 @@
     <t>echo</t>
   </si>
   <si>
-    <t>https://www.echo-usa.com/globalassets/echo-logo.svg</t>
-  </si>
-  <si>
     <t>Discover Echo professional outdoor power equipment, blowers, trimmers, and chainsaws.</t>
   </si>
   <si>
@@ -1509,9 +1353,6 @@
     <t>eibenstock</t>
   </si>
   <si>
-    <t>https://www.eibenstock.com/fileadmin/templates/images/logo.svg</t>
-  </si>
-  <si>
     <t>Browse Eibenstock specialist professional power tools, core drills, and concrete grinders.</t>
   </si>
   <si>
@@ -1527,9 +1368,6 @@
     <t>starrett</t>
   </si>
   <si>
-    <t>https://www.starrett.com/globalassets/starrett-logo.svg</t>
-  </si>
-  <si>
     <t>Explore Starrett precision measuring instruments, hole saws, hack saws, and layout tools.</t>
   </si>
   <si>
@@ -1545,9 +1383,6 @@
     <t>kennedy</t>
   </si>
   <si>
-    <t>https://www.kennedy-tools.co.uk/images/logo.svg</t>
-  </si>
-  <si>
     <t>Discover Kennedy industrial hand tools, workshop storage solutions, and cutting equipment.</t>
   </si>
   <si>
@@ -1563,9 +1398,6 @@
     <t>solis-solar</t>
   </si>
   <si>
-    <t>https://www.ginlong.com/images/solis-logo.png</t>
-  </si>
-  <si>
     <t>Browse Ginlong Solis grid-tied solar inverters, hybrid inverters, and PV monitoring systems.</t>
   </si>
   <si>
@@ -1573,6 +1405,174 @@
   </si>
   <si>
     <t>Explore Solis solar inverters, residential and commercial renewable energy solutions.</t>
+  </si>
+  <si>
+    <t>https://images.seeklogo.com/logo-png/2/2/bosch-logo-png_seeklogo-21523.png</t>
+  </si>
+  <si>
+    <t>https://formula1wax.com/cdn/shop/files/Formula_1_Logo_simplified.png?v=1711723097&amp;width=270</t>
+  </si>
+  <si>
+    <t>https://www.3mindia.in/3m_theme_assets/themes/3MTheme/assets/images/unicorn/Logo_mobile.png</t>
+  </si>
+  <si>
+    <t>https://www.meguiars.com/themes/custom/meg/logo.png</t>
+  </si>
+  <si>
+    <t>https://turtlewax.in/cdn/shop/files/turtle-wax-logo_6ec84b4e-6cde-4eb5-8e63-9054c95af401_png.png?v=1699528518&amp;width=135</t>
+  </si>
+  <si>
+    <t>https://makita.in/wp-content/themes/Makita/img/logo.jpg</t>
+  </si>
+  <si>
+    <t>https://www.dewalt.com/_next/image?url=https%3A%2F%2Fbynder.sbdinc.com%2Ftransform%2F1d28105f-0bcc-4c55-816c-bbb190fbdf02%2FDW_Y-ON-B_LMB1%3Fio%3Dtransform%253Afit%252Cwidth%253A256%26format%3Dwebp%26quality%3D75&amp;w=256&amp;q=75</t>
+  </si>
+  <si>
+    <t>https://www.hilti.in/static/ui/assets/images/hilti-logo.svg</t>
+  </si>
+  <si>
+    <t>https://hikoki-powertools.in/common/images/common/logo/logo.png</t>
+  </si>
+  <si>
+    <t>https://www.blackanddecker.com/cdn/shop/t/182/assets/Logo-Grey.svg?v=146770065678055879911727771188</t>
+  </si>
+  <si>
+    <t>https://jksuperdrive.com/wp-content/uploads/2021/06/JK-Maini-Logo-Updated.png</t>
+  </si>
+  <si>
+    <t>https://www.kpt.co.in/logo-full.svg</t>
+  </si>
+  <si>
+    <t>https://www.endicopowertools.com/public/img/logo.png</t>
+  </si>
+  <si>
+    <t>https://ralliwolf.com/wp-content/themes/ralliwolf/images/logo.png</t>
+  </si>
+  <si>
+    <t>https://www.waaree.com/_next/image/?url=%2Fupload%2Fmedia%2Fimage_1_1_1749036191.png&amp;w=256&amp;q=85</t>
+  </si>
+  <si>
+    <t>https://www.vikramsolar.com/wp-content/uploads/2022/04/cropped-logo-1.png.webp</t>
+  </si>
+  <si>
+    <t>https://dg4e57nn4fnta.cloudfront.net/logos/ReNew_White-nospace.svg</t>
+  </si>
+  <si>
+    <t>https://d32zxht0g2dn3w.cloudfront.net/s3fs-public/2023-12/logo%201.png</t>
+  </si>
+  <si>
+    <t>https://docs.exideindustries.com/images/logo.png</t>
+  </si>
+  <si>
+    <t>https://amaron-prod-images.s3.ap-south-1.amazonaws.com/s3fs-public/Amaron_Logo_0.jpg</t>
+  </si>
+  <si>
+    <t>https://vectorseek.com/wp-content/uploads/2023/04/Milwaukee-Tool-Logo-Vector.jpg</t>
+  </si>
+  <si>
+    <t>https://www.dongchengtool.com/_nuxt/img/logo.c0f8da1.png</t>
+  </si>
+  <si>
+    <t>https://www.dcatools.com/_nuxt/img/logo.3519305.png</t>
+  </si>
+  <si>
+    <t>https://assets.cdn.festool.io/festool-logo.min.svg</t>
+  </si>
+  <si>
+    <t>https://www.dremel.com/images/dremel_w340-png--16fe15ef3de449c0a6662896569f4483.png?imgWidth=340&amp;imgHeight=111&amp;scale=1</t>
+  </si>
+  <si>
+    <t>https://groz-tools.com/media/logo/stores/2/logo.png</t>
+  </si>
+  <si>
+    <t>https://www.freemansgroup.com/wp-content/uploads/2026/04/FREEMANS-LOGO-28th-april-1.jpg</t>
+  </si>
+  <si>
+    <t>https://www.cumi-murugappa.com/abrasives/wp-content/themes/cumi/images/logo.png</t>
+  </si>
+  <si>
+    <t>https://wavex.in/cdn/shop/files/wavex_auto_care_logo.png?format=webp&amp;height=331&amp;v=1774253426</t>
+  </si>
+  <si>
+    <t>https://tse2.mm.bing.net/th/id/OIP.Cb3xoLYLZWPahEtUenm6OAHaCo?r=0&amp;rs=1&amp;pid=ImgDetMain&amp;o=7&amp;rm=3</t>
+  </si>
+  <si>
+    <t>https://www.chemicalguys.com/cdn/shop/files/chemical-guys-logo.svg?v=1682352461&amp;width=352</t>
+  </si>
+  <si>
+    <t>https://www.waxpol.com/images/logo.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0268/2352/4429/t/12/assets/33ebad748be1--img-logo-mothers-classic.png?v=1579901803</t>
+  </si>
+  <si>
+    <t>https://shinexpro.in/cdn/shop/files/SXP_Logo_3png_file_180x.png?v=1619420596</t>
+  </si>
+  <si>
+    <t>https://goldisolar.com/wp-content/uploads/2022/04/Goldi-Solar-Logo_white.svg</t>
+  </si>
+  <si>
+    <t>https://www.premierenergies.com/static/media/premier-energies.b1bb2f7bbecd36942cfa.png</t>
+  </si>
+  <si>
+    <t>https://www.microtek.in/img/logo.svg</t>
+  </si>
+  <si>
+    <t>https://havells.com/media/logo/stores/1/Havells_Logo.svg</t>
+  </si>
+  <si>
+    <t>https://www.servotech.in/_next/image?url=https%3A%2F%2Fwww.servotech.in%2Fblog%2Fwp-content%2Fuploads%2F2023%2F04%2Flogo.png&amp;w=256&amp;q=75</t>
+  </si>
+  <si>
+    <t>https://www.su-kam.com/wp-content/uploads/2024/06/Untitled-design.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/Ryobi_company_logo.svg/250px-Ryobi_company_logo.svg.png</t>
+  </si>
+  <si>
+    <t>https://atozshop.co.in/wp-content/uploads/2026/06/LOGO-01-755x218.webp</t>
+  </si>
+  <si>
+    <t>https://media.fischer.group/v7/_media-prod_/national/samples/logos/logo-footer.png?h=30&amp;func=bound</t>
+  </si>
+  <si>
+    <t>https://fein.com/_assets/5b177ecb5a6853f1f7888e098b205f4e/Images/main/layout/logo.svg</t>
+  </si>
+  <si>
+    <t>https://www.atlascopco.com/etc.clientlibs/settings/wcm/designs/accommons/design-system/clientlib-assets/resources/icons/logo.svg</t>
+  </si>
+  <si>
+    <t>https://saatvikgroup.com/wp-content/uploads/2026/06/web-banner-02-3-scaled.png</t>
+  </si>
+  <si>
+    <t>f7d549_792ca485cfa042429d37c4a6ba3b2a29~mv2_d_3004_1496_s_2.png (185×80) (wixstatic.com)</t>
+  </si>
+  <si>
+    <t>https://kenbrooksolar.com/wp-content/uploads/Patanjali-Solar-Panels-System-Inverter-Pumps-All-Products-Price-List.jpg</t>
+  </si>
+  <si>
+    <t>https://www.skil.com/cdn/shop/files/skil-logo.svg?v=1750635650&amp;width=150</t>
+  </si>
+  <si>
+    <t>https://be.prod.metabo.com/Global/Metabo-Logo/Metabo-Logo-2_green-on-transparent/Metabo-Logo-2_C_green-on-transparent_no-claim_no-copyright.png</t>
+  </si>
+  <si>
+    <t>https://www.stihl.in/content/experience-fragments/stihl/in/en/main_navigation/master/_jcr_content/root/mainnav/logo.coreimg.svg/1686828280355/stihl-logo.svg</t>
+  </si>
+  <si>
+    <t>https://www.echo-india.com/_nuxt/img/c6d89ae.svg</t>
+  </si>
+  <si>
+    <t>https://www.eibenstock.com/templates/eibenstock-2023/img/logo.png</t>
+  </si>
+  <si>
+    <t>https://www.starrett.com/images/default-source/logos/starrett-logo-red.png?sfvrsn=1f2ac5db_3</t>
+  </si>
+  <si>
+    <t>https://static-content.cromwell.co.uk/content/images/brands/kennedy/KENNEDY_RGB_Master-Red.webp</t>
+  </si>
+  <si>
+    <t>https://cmsdata.solisinverters.com/uploads/image/5bdc25d94070b.png</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1651,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1669,6 +1669,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2030,7 +2034,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2044,13 +2048,16 @@
   <dimension ref="A1:G125"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="29.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.21875" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="28.8">
+    <row r="1" spans="1:7" s="6" customFormat="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2073,14 +2080,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="100.8">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="28.8">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>153</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2096,14 +2103,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="3" spans="1:7" s="3" customFormat="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="7" t="s">
         <v>154</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2119,14 +2126,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="4" spans="1:7" s="3" customFormat="1">
       <c r="A4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -2142,14 +2149,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="5" spans="1:7" s="3" customFormat="1">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>156</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2165,14 +2172,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="129.6">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="28.8">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2188,7 +2195,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="7" spans="1:7" s="3" customFormat="1">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -2211,14 +2218,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="3" customFormat="1" ht="43.2">
+    <row r="8" spans="1:7" s="3" customFormat="1">
       <c r="A8" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2234,14 +2241,14 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="9" spans="1:7" s="3" customFormat="1">
       <c r="A9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2257,7 +2264,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="10" spans="1:7" s="3" customFormat="1">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -2280,7 +2287,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="11" spans="1:7" s="3" customFormat="1">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -2303,7 +2310,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="12" spans="1:7" s="3" customFormat="1">
       <c r="A12" s="3" t="s">
         <v>78</v>
       </c>
@@ -2326,7 +2333,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="13" spans="1:7" s="3" customFormat="1">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
@@ -2349,7 +2356,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="14" spans="1:7" s="3" customFormat="1">
       <c r="A14" s="3" t="s">
         <v>86</v>
       </c>
@@ -2372,7 +2379,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="3" customFormat="1" ht="43.2">
+    <row r="15" spans="1:7" s="3" customFormat="1">
       <c r="A15" s="3" t="s">
         <v>91</v>
       </c>
@@ -2395,7 +2402,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="16" spans="1:7" s="3" customFormat="1">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2418,7 +2425,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="17" spans="1:7" s="3" customFormat="1">
       <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
@@ -2441,7 +2448,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="18" spans="1:7" s="3" customFormat="1">
       <c r="A18" s="3" t="s">
         <v>104</v>
       </c>
@@ -2449,7 +2456,7 @@
         <v>105</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>169</v>
+        <v>455</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>35</v>
@@ -2464,7 +2471,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="3" customFormat="1" ht="43.2">
+    <row r="19" spans="1:7" s="3" customFormat="1">
       <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
@@ -2472,7 +2479,7 @@
         <v>109</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>40</v>
@@ -2487,7 +2494,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="20" spans="1:7" s="3" customFormat="1">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -2495,7 +2502,7 @@
         <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -2510,7 +2517,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="21" spans="1:7" s="3" customFormat="1">
       <c r="A21" s="3" t="s">
         <v>117</v>
       </c>
@@ -2518,7 +2525,7 @@
         <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>40</v>
@@ -2533,15 +2540,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="22" spans="1:7" s="3" customFormat="1">
       <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>172</v>
+      <c r="C22" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>40</v>
@@ -2556,7 +2563,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="3" customFormat="1" ht="86.4">
+    <row r="23" spans="1:7" s="3" customFormat="1" ht="28.8">
       <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
@@ -2564,7 +2571,7 @@
         <v>126</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>35</v>
@@ -2579,7 +2586,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="24" spans="1:7" s="3" customFormat="1">
       <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
@@ -2587,7 +2594,7 @@
         <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>35</v>
@@ -2602,7 +2609,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="25" spans="1:7" s="3" customFormat="1">
       <c r="A25" s="3" t="s">
         <v>21</v>
       </c>
@@ -2610,7 +2617,7 @@
         <v>134</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>35</v>
@@ -2625,7 +2632,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="26" spans="1:7" s="3" customFormat="1">
       <c r="A26" s="3" t="s">
         <v>22</v>
       </c>
@@ -2633,7 +2640,7 @@
         <v>138</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>35</v>
@@ -2648,7 +2655,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="27" spans="1:7" s="3" customFormat="1">
       <c r="A27" s="3" t="s">
         <v>23</v>
       </c>
@@ -2656,7 +2663,7 @@
         <v>142</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>35</v>
@@ -2671,7 +2678,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="3" customFormat="1" ht="43.2">
+    <row r="28" spans="1:7" s="3" customFormat="1">
       <c r="A28" s="3" t="s">
         <v>25</v>
       </c>
@@ -2679,7 +2686,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>40</v>
@@ -2694,7 +2701,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="3" customFormat="1" ht="72">
+    <row r="29" spans="1:7" s="3" customFormat="1">
       <c r="A29" s="3" t="s">
         <v>26</v>
       </c>
@@ -2702,7 +2709,7 @@
         <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>40</v>
@@ -2717,1269 +2724,1269 @@
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="3" customFormat="1" ht="57.6">
+    <row r="30" spans="1:7" s="3" customFormat="1">
       <c r="A30" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>204</v>
+        <v>456</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F30" s="3" t="s">
+    </row>
+    <row r="31" spans="1:7" s="3" customFormat="1">
+      <c r="A31" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" s="3" customFormat="1" ht="57.6">
-      <c r="A31" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>210</v>
+        <v>457</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="3" customFormat="1">
+      <c r="A32" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="3" customFormat="1" ht="57.6">
-      <c r="A32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>215</v>
+      <c r="C32" s="7" t="s">
+        <v>458</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="3" customFormat="1" ht="58.2" thickBot="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="3" customFormat="1" ht="29.4" thickBot="1">
       <c r="A33" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>459</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="55.8" thickBot="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1">
       <c r="A34" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>225</v>
+        <v>460</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="55.8" thickBot="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="43.8" thickBot="1">
       <c r="A35" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>230</v>
+        <v>461</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1">
+      <c r="A36" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="F35" s="4" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1">
+      <c r="A37" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="187.8" thickBot="1">
-      <c r="A36" s="4" t="s">
+      <c r="C37" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E36" s="4" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1">
+      <c r="A38" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A37" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="58.2" thickBot="1">
-      <c r="A38" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="C38" s="5" t="s">
-        <v>248</v>
+        <v>464</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A39" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1">
+      <c r="A40" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F40" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A39" s="4" t="s">
+    <row r="41" spans="1:7" ht="15" thickBot="1">
+      <c r="A41" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B41" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C41" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="4" t="s">
+      <c r="F41" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="G39" s="4" t="s">
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1">
+      <c r="A42" s="4" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="42" thickBot="1">
-      <c r="A40" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="C42" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F40" s="4" t="s">
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1">
+      <c r="A43" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A41" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="69.599999999999994" thickBot="1">
-      <c r="A42" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A43" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>277</v>
-      </c>
       <c r="C43" s="5" t="s">
-        <v>278</v>
+        <v>469</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="72.599999999999994" thickBot="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1">
       <c r="A44" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>283</v>
+        <v>470</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="55.8" thickBot="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1">
       <c r="A45" s="4" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>289</v>
+        <v>471</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="58.2" thickBot="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1">
       <c r="A46" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>294</v>
+        <v>472</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="55.8" thickBot="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1">
       <c r="A47" s="4" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>300</v>
+        <v>281</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>473</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="43.8" thickBot="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1">
       <c r="A48" s="4" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>306</v>
+        <v>474</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1">
       <c r="A49" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>311</v>
+        <v>475</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="58.2" thickBot="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>316</v>
+        <v>476</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1">
       <c r="A51" s="4" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>322</v>
+        <v>477</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="83.4" thickBot="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="55.8" thickBot="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="29.4" thickBot="1">
       <c r="A53" s="4" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>333</v>
+        <v>479</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1">
       <c r="A54" s="4" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>339</v>
+        <v>480</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="55.8" thickBot="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1">
       <c r="A55" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>344</v>
+        <v>481</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="55.8" thickBot="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1">
       <c r="A56" s="4" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>350</v>
+        <v>482</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1">
       <c r="A57" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>355</v>
+        <v>483</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="87" thickBot="1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1">
       <c r="A59" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>365</v>
+        <v>485</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="55.8" thickBot="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1">
       <c r="A60" s="4" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>371</v>
+        <v>486</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="29.4" thickBot="1">
       <c r="A61" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>376</v>
+        <v>487</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1">
       <c r="A62" s="4" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>382</v>
+        <v>488</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="58.2" thickBot="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1">
       <c r="A63" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>387</v>
+        <v>489</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="55.8" thickBot="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1">
       <c r="A64" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>392</v>
+        <v>490</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1">
       <c r="A65" s="4" t="s">
-        <v>396</v>
+        <v>360</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>398</v>
+        <v>491</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="55.8" thickBot="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1">
       <c r="A66" s="4" t="s">
-        <v>402</v>
+        <v>365</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>404</v>
+        <v>492</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>406</v>
+        <v>368</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="72.599999999999994" thickBot="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="29.4" thickBot="1">
       <c r="A67" s="4" t="s">
-        <v>408</v>
+        <v>370</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>409</v>
+        <v>371</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>410</v>
+        <v>493</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="55.8" thickBot="1">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" thickBot="1">
       <c r="A68" s="4" t="s">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>416</v>
+        <v>494</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>418</v>
+        <v>378</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="55.8" thickBot="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1">
       <c r="A69" s="4" t="s">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="55.8" thickBot="1">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" thickBot="1">
       <c r="A70" s="4" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>429</v>
+        <v>387</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>430</v>
+        <v>388</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="58.2" thickBot="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" thickBot="1">
       <c r="A71" s="4" t="s">
-        <v>432</v>
+        <v>390</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>433</v>
+        <v>391</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>434</v>
+        <v>497</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>435</v>
+        <v>392</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1">
       <c r="A72" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>438</v>
+        <v>395</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>439</v>
+        <v>498</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="72.599999999999994" thickBot="1">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="29.4" thickBot="1">
       <c r="A73" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="58.2" thickBot="1">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="28.2" thickBot="1">
       <c r="A74" s="4" t="s">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>449</v>
+        <v>404</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="55.8" thickBot="1">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15" thickBot="1">
       <c r="A75" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>455</v>
+        <v>408</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>501</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="58.2" thickBot="1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15" thickBot="1">
       <c r="A76" s="4" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>462</v>
+        <v>414</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>463</v>
+        <v>415</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="55.8" thickBot="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" thickBot="1">
       <c r="A77" s="4" t="s">
-        <v>465</v>
+        <v>417</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>466</v>
+        <v>418</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>468</v>
+        <v>419</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>469</v>
+        <v>420</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="29.4" thickBot="1">
       <c r="A78" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>471</v>
+        <v>422</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>473</v>
+        <v>423</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="55.8" thickBot="1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="29.4" thickBot="1">
       <c r="A79" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>476</v>
+        <v>426</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>478</v>
+        <v>427</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>479</v>
+        <v>428</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="55.8" thickBot="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickBot="1">
       <c r="A80" s="4" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>482</v>
+        <v>431</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>484</v>
+        <v>432</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>485</v>
+        <v>433</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="58.2" thickBot="1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" thickBot="1">
       <c r="A81" s="4" t="s">
-        <v>487</v>
+        <v>435</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>488</v>
+        <v>436</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>490</v>
+        <v>437</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>491</v>
+        <v>438</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="55.8" thickBot="1">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" thickBot="1">
       <c r="A82" s="4" t="s">
-        <v>493</v>
+        <v>440</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>494</v>
+        <v>441</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" thickBot="1">
       <c r="A83" s="4" t="s">
-        <v>499</v>
+        <v>445</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>500</v>
+        <v>446</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>502</v>
+        <v>447</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>503</v>
+        <v>448</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="69.599999999999994" thickBot="1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1">
       <c r="A84" s="4" t="s">
-        <v>505</v>
+        <v>450</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>506</v>
+        <v>451</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>508</v>
+        <v>452</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>509</v>
+        <v>453</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>510</v>
+        <v>454</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4102,7 +4109,7 @@
     <hyperlink ref="C3" r:id="rId2" xr:uid="{DA1DC669-C49A-4C9B-BCFA-5C572AF12A7F}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{8DE281CE-B03A-4D8C-B243-A38398917470}"/>
     <hyperlink ref="C5" r:id="rId4" xr:uid="{0F5EFF59-5397-4B15-A68F-7E229731C6AF}"/>
-    <hyperlink ref="C6" r:id="rId5" display="https://static.wixstatic.com/media/e97088_d0c8e8ddda36461cace1e6ccadfc8b7f~mv2.jpg/v1/fill/w_374,h_110,al_c,q_80,usm_0.66_1.00_0.01,enc_avif,quality_auto/Camron Logo_edited.jpg" xr:uid="{271E1ECA-016B-4501-83AD-7610A398EFE1}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{271E1ECA-016B-4501-83AD-7610A398EFE1}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{56D09FB7-F2E5-431C-A977-6884FC29A889}"/>
     <hyperlink ref="C8" r:id="rId7" xr:uid="{EF297E98-C6D9-46AA-A78B-84E3AB3DCA0A}"/>
     <hyperlink ref="C9" r:id="rId8" xr:uid="{C89771F0-F5A9-42F1-A8BF-B7E0D0D90109}"/>
@@ -4114,71 +4121,17 @@
     <hyperlink ref="C15" r:id="rId14" xr:uid="{FF5EEB5E-F9B5-4343-B3E4-F8B1DA1D4B90}"/>
     <hyperlink ref="C16" r:id="rId15" xr:uid="{38576126-7773-46EB-ABAD-97725EF1D75A}"/>
     <hyperlink ref="C17" r:id="rId16" xr:uid="{1823EFF0-5AE7-47AD-B37A-CC8505C27457}"/>
-    <hyperlink ref="C18" r:id="rId17" xr:uid="{604E9CEA-AD24-4251-8387-6E8B42A3B89E}"/>
-    <hyperlink ref="C20" r:id="rId18" xr:uid="{3D0EF484-132B-4B29-B696-F19E32E45BF6}"/>
-    <hyperlink ref="C21" r:id="rId19" xr:uid="{1D192599-64AE-499B-BBB3-78FADE93ACE1}"/>
-    <hyperlink ref="C22" r:id="rId20" xr:uid="{1632554B-1E6A-4FFC-AC08-CC99D8C46B43}"/>
-    <hyperlink ref="C23" r:id="rId21" xr:uid="{A426DA0E-5ECC-428A-9E0F-79AFBDFDC0A1}"/>
-    <hyperlink ref="C24" r:id="rId22" xr:uid="{E131E37A-2710-41A9-8E09-385A48A22B6E}"/>
-    <hyperlink ref="C25" r:id="rId23" xr:uid="{619AAEF6-A880-4FF2-A6A1-9AAED52AA7C3}"/>
-    <hyperlink ref="C26" r:id="rId24" xr:uid="{65B04FD4-E0D6-4862-8502-4BF8E1730BA5}"/>
-    <hyperlink ref="C27" r:id="rId25" xr:uid="{85DD1AA7-7AAF-433F-B7CD-6FC2603C7066}"/>
-    <hyperlink ref="C29" r:id="rId26" xr:uid="{023EBDAF-B529-4349-A162-0526693D85BA}"/>
-    <hyperlink ref="C30" r:id="rId27" display="https://www.google.com/search?q=https%3A%2F%2Fm.media-amazon.com%2Fimages%2FI%2F31q82B7aLKL._AC_.jpg" xr:uid="{1B9622F9-CCE1-4C61-81D3-0CE8C213D5CB}"/>
-    <hyperlink ref="C31" r:id="rId28" display="https://www.google.com/search?q=https://www.3m.com/3M/en_US/p/d/b00038555/" xr:uid="{7B93C535-153D-4A6F-951B-A847717D7D50}"/>
-    <hyperlink ref="C32" r:id="rId29" display="https://www.google.com/search?q=https://www.meguiars.com/sites/default/files/styles/logo/public/meguiars-logo.png" xr:uid="{1A59EE14-C00C-48F7-96B5-8F305DB4B3E1}"/>
-    <hyperlink ref="C33" r:id="rId30" display="https://www.google.com/search?q=https://www.turtlewax.com/cdn/shop/files/TurtleWax_Logo_2020_Black_300x.png" xr:uid="{D4FEAF10-90C6-4653-965F-6853D0345B4F}"/>
-    <hyperlink ref="C34" r:id="rId31" display="https://www.google.com/search?q=https://www.makita.co.in/themes/makita/assets/images/logo.png" xr:uid="{FD59263B-D5B7-4324-ABE9-61F1A708E098}"/>
-    <hyperlink ref="C35" r:id="rId32" display="https://www.google.com/search?q=https://www.dewalt.com/globalassets/dewalt/logo.svg" xr:uid="{ED96214F-39AC-4665-A16E-10F4F4574662}"/>
-    <hyperlink ref="C36" r:id="rId33" display="https://www.google.com/search?q=https://www.hilti.group/medias/hilti-logo.svg%3Fcontext%3DbWFzdGVyfHJvb3R8MTU4NHxhcHBsaWNhdGlvbi9zdmd8aDg0L2g5My84ODgxMTQ1MzM1MzI2LnN2Z3xkNDExNTA3Y2M2YzgzMmFiYzI5MDcyNDcyYzRiNDFjMDliMTEzMmZkMTBiMWJmZjA0MWU5OWQ3MWE4YzgwMTNk" xr:uid="{81FCC64A-2129-43BA-A2E9-5E0E2C31BCE1}"/>
-    <hyperlink ref="C37" r:id="rId34" display="https://www.google.com/search?q=https://www.hikoki-powertools.com/common/images/logo.svg" xr:uid="{3FED8A3E-A3DC-4AF0-A4DF-41015CC14851}"/>
-    <hyperlink ref="C38" r:id="rId35" display="https://www.google.com/search?q=https://www.blackanddecker.com/globalassets/black-and-decker/logo.svg" xr:uid="{6FEA8AD6-B684-452F-9B5A-82CE99631BDF}"/>
-    <hyperlink ref="C39" r:id="rId36" display="https://www.google.com/search?q=https://www.jkfiles.com/assets/images/logo.png" xr:uid="{3105DCB7-568C-4CD8-AB39-6C77A61BF366}"/>
-    <hyperlink ref="C40" r:id="rId37" display="https://www.google.com/search?q=https://www.kpt.co.in/images/logo.png" xr:uid="{992C7E83-28FF-4030-A442-2DB7D69AF948}"/>
-    <hyperlink ref="C41" r:id="rId38" display="https://www.google.com/search?q=https://www.endicotools.com/images/logo.png" xr:uid="{19A0873A-3277-4366-9C3A-56E12D1F0BFC}"/>
-    <hyperlink ref="C42" r:id="rId39" display="https://www.google.com/search?q=https://ralliwolf.com/wp-content/uploads/2021/03/logo.png" xr:uid="{2EE44E54-8333-41D2-A254-30D9547DB8FA}"/>
-    <hyperlink ref="C43" r:id="rId40" display="https://www.google.com/search?q=https://www.waaree.com/images/waaree-logo.png" xr:uid="{FE751C54-1352-4B8D-BBA6-D9FA9E8BA48C}"/>
-    <hyperlink ref="C44" r:id="rId41" display="https://www.google.com/search?q=https://www.vikramsolar.com/wp-content/uploads/2021/03/vikram-solar-logo.png" xr:uid="{EAEE8EF6-0D6E-4FFA-91EB-0AAAFC641B6B}"/>
-    <hyperlink ref="C45" r:id="rId42" display="https://www.google.com/search?q=https://renew.com/wp-content/uploads/2023/04/renew-logo.svg" xr:uid="{5FC1F1BB-76BF-450D-969B-122821ADBC16}"/>
-    <hyperlink ref="C46" r:id="rId43" display="https://www.google.com/search?q=https://www.panasonic.com/content/dam/global/common/panasonic-logo.svg" xr:uid="{833220CD-0511-4647-9205-168D677D07C1}"/>
-    <hyperlink ref="C47" r:id="rId44" display="https://www.google.com/search?q=https://www.exideindustries.com/images/exide-logo.png" xr:uid="{EA0AA9B6-3668-4C1A-B4E7-43041E9D4675}"/>
-    <hyperlink ref="C48" r:id="rId45" display="https://www.google.com/search?q=https://www.amaron.in/images/amaron-logo.png" xr:uid="{B3B21DCF-771C-4F83-BA0A-DACCDF1B4C19}"/>
-    <hyperlink ref="C49" r:id="rId46" display="https://www.google.com/search?q=https://www.milwaukeetool.com/Content/Images/header-logo.svg" xr:uid="{A7AC2AAD-F57A-4D3A-A56A-3688724693E4}"/>
-    <hyperlink ref="C50" r:id="rId47" display="https://www.google.com/search?q=https://www.dongchengtool.com/upload/20220623/1655974070.png" xr:uid="{9226EB91-2983-4045-9A02-760AD3078FBC}"/>
-    <hyperlink ref="C51" r:id="rId48" display="https://www.google.com/search?q=https://www.dcatools.com/images/logo.png" xr:uid="{578003DD-265C-4FDB-8913-38700183080C}"/>
-    <hyperlink ref="C52" r:id="rId49" display="https://www.google.com/search?q=https://www.festool.com/assets/images/festool-logo.svg" xr:uid="{F03877C9-1A9B-4916-BF06-E3C02352D75E}"/>
-    <hyperlink ref="C53" r:id="rId50" display="https://www.google.com/search?q=https://www.dremel.com/static/dremel-logo.svg" xr:uid="{742FAAE0-E5F2-4D49-AD98-9830774E7C95}"/>
-    <hyperlink ref="C54" r:id="rId51" display="https://www.google.com/search?q=https://www.groz-tools.com/media/logo/stores/1/GROZ_Logo_Red_Black_1.png" xr:uid="{BDF273B5-705F-47C7-B7B4-D8D471A87D54}"/>
-    <hyperlink ref="C55" r:id="rId52" display="https://www.google.com/search?q=https://freemans.net/images/logo.png" xr:uid="{C13CE459-6FA3-44F7-9DAE-49F7A4E5FF8C}"/>
-    <hyperlink ref="C56" r:id="rId53" display="https://www.google.com/search?q=https://www.cumi-muri.com/images/cumi-logo.png" xr:uid="{BD9B5573-D44D-4BFE-AC60-CC3384563BBC}"/>
-    <hyperlink ref="C57" r:id="rId54" display="https://www.google.com/search?q=https://wavex.in/cdn/shop/files/logo_180x.png" xr:uid="{2734B9DE-FBD0-41B4-ACDC-4609327BB0B7}"/>
-    <hyperlink ref="C58" r:id="rId55" display="https://www.google.com/search?q=https://www.sonax.com/fileadmin/templates/images/sonax-logo.svg" xr:uid="{9147FE49-877C-4A7C-9E93-05DE3204E174}"/>
-    <hyperlink ref="C59" r:id="rId56" display="https://www.google.com/search?q=https://www.chemicalguys.com/on/demandware.static/Sites-CG-Site/-/default/dw8374828b/images/cg-logo.svg" xr:uid="{B05AEC87-ED10-499A-B084-DC3C65C09849}"/>
-    <hyperlink ref="C60" r:id="rId57" display="https://www.google.com/search?q=https://www.waxpol.com/images/logo.png" xr:uid="{56B35AD3-DE05-4790-9B41-9B371C990DCD}"/>
-    <hyperlink ref="C61" r:id="rId58" display="https://www.google.com/search?q=https://mothers.com/cdn/shop/files/mothers-logo_180x.png" xr:uid="{53577D6D-4F6B-4338-BD61-DA33C698204F}"/>
-    <hyperlink ref="C62" r:id="rId59" display="https://www.google.com/search?q=https://shinexpro.in/cdn/shop/files/shinexpro_logo_180x.png" xr:uid="{28757B15-33B0-4729-BB5D-563094C1225E}"/>
-    <hyperlink ref="C63" r:id="rId60" display="https://www.google.com/search?q=https://goldisolar.com/wp-content/uploads/2023/03/goldi-logo.png" xr:uid="{BCCDE8EC-1ACF-41F7-B028-432DF5152680}"/>
-    <hyperlink ref="C64" r:id="rId61" display="https://www.google.com/search?q=https://premierenergies.com/images/logo.png" xr:uid="{BDA4C34A-ED22-4827-9266-AAC5031DAE10}"/>
-    <hyperlink ref="C65" r:id="rId62" display="https://www.google.com/search?q=https://www.microtekdirect.com/images/logo.png" xr:uid="{6E4CA772-E471-48F9-B061-0AD32DBFAC96}"/>
-    <hyperlink ref="C66" r:id="rId63" display="https://www.google.com/search?q=https://www.havells.com/images/havells-logo.svg" xr:uid="{DB289A11-B589-43BF-A4E5-244F9B90AC16}"/>
-    <hyperlink ref="C67" r:id="rId64" display="https://www.google.com/search?q=https://servotech.in/wp-content/uploads/2022/01/servotech-logo.png" xr:uid="{78EEE294-14E0-4CC0-9A35-E5DD894A3738}"/>
-    <hyperlink ref="C68" r:id="rId65" display="https://www.google.com/search?q=https://www.su-kam.com/images/su-kam-logo.png" xr:uid="{9A393C89-D3B7-4EF8-9286-1EAEEA533037}"/>
-    <hyperlink ref="C69" r:id="rId66" display="https://www.google.com/search?q=https://www.ryobitools.com/medias/ryobi-logo.svg" xr:uid="{490288EE-AF63-452A-B7D5-C02EBE10836C}"/>
-    <hyperlink ref="C70" r:id="rId67" display="https://www.google.com/search?q=https://krost.in/cdn/shop/files/krost-logo.png" xr:uid="{56A33686-72E9-4FD3-B083-5D349AAC4774}"/>
-    <hyperlink ref="C71" r:id="rId68" display="https://www.google.com/search?q=https://www.fischer.de/fischer-en/-/media/fischer-group/fischer-logo.svg" xr:uid="{8E85E127-6596-475F-B722-28842E6F0E4D}"/>
-    <hyperlink ref="C72" r:id="rId69" display="https://www.google.com/search?q=https://fein.com/assets/images/fein-logo.svg" xr:uid="{E7941CB9-EDBB-4738-8D58-5A34ED53E43F}"/>
-    <hyperlink ref="C73" r:id="rId70" display="https://www.google.com/search?q=https://www.atlascopco.com/content/dam/atlas-copco/global/logos/atlas-copco-logo.svg" xr:uid="{03519C7E-8974-4D7C-9857-56EB90F38CE1}"/>
-    <hyperlink ref="C74" r:id="rId71" display="https://www.google.com/search?q=https://saatvikgroup.com/wp-content/uploads/2023/07/saatvik-logo.png" xr:uid="{6A5F8658-3F8E-4D89-84D2-56C95686DB30}"/>
-    <hyperlink ref="C75" r:id="rId72" display="https://www.google.com/search?q=https://www.renewsysworld.com/images/renewsys-logo.png" xr:uid="{90B76089-4655-4C51-8CEB-C5405D5390C1}"/>
-    <hyperlink ref="C76" r:id="rId73" display="https://www.google.com/search?q=https://www.patanjaliayurved.net/assets/images/patanjali-logo.png" xr:uid="{1079E9E1-B1F0-473C-8259-7909C852705C}"/>
-    <hyperlink ref="C77" r:id="rId74" display="https://www.google.com/search?q=https://www.skil.com/globalassets/skil/logo.svg" xr:uid="{A6AD9A2B-CE09-4BC2-AF7D-9F680D431E7E}"/>
-    <hyperlink ref="C78" r:id="rId75" display="https://www.google.com/search?q=https://www.metabo.com/medias/metabo-logo.svg" xr:uid="{2C81986A-67DE-4F52-A451-974006CAD72E}"/>
-    <hyperlink ref="C79" r:id="rId76" display="https://www.google.com/search?q=https://www.stihl.com/assets/images/stihl-logo.svg" xr:uid="{FBEB5890-06C3-4DED-9311-FF8EBAE4A683}"/>
-    <hyperlink ref="C80" r:id="rId77" display="https://www.google.com/search?q=https://www.echo-usa.com/globalassets/echo-logo.svg" xr:uid="{90698BEC-606F-4459-8FEC-9D4F52945E6B}"/>
-    <hyperlink ref="C81" r:id="rId78" display="https://www.google.com/search?q=https://www.eibenstock.com/fileadmin/templates/images/logo.svg" xr:uid="{B2E0D824-D938-4BB4-AA39-DC963D9ADD8B}"/>
-    <hyperlink ref="C82" r:id="rId79" display="https://www.google.com/search?q=https://www.starrett.com/globalassets/starrett-logo.svg" xr:uid="{041C250D-CAB6-488F-B8CE-303F205D0EA3}"/>
-    <hyperlink ref="C83" r:id="rId80" display="https://www.google.com/search?q=https://www.kennedy-tools.co.uk/images/logo.svg" xr:uid="{9346F320-6852-4969-BB35-A2E6003D3609}"/>
-    <hyperlink ref="C84" r:id="rId81" display="https://www.google.com/search?q=https://www.ginlong.com/images/solis-logo.png" xr:uid="{4170BB3F-F8EC-49BB-BE39-383A04F9EFCE}"/>
+    <hyperlink ref="C20" r:id="rId17" xr:uid="{3D0EF484-132B-4B29-B696-F19E32E45BF6}"/>
+    <hyperlink ref="C21" r:id="rId18" xr:uid="{1D192599-64AE-499B-BBB3-78FADE93ACE1}"/>
+    <hyperlink ref="C22" r:id="rId19" xr:uid="{1632554B-1E6A-4FFC-AC08-CC99D8C46B43}"/>
+    <hyperlink ref="C23" r:id="rId20" xr:uid="{A426DA0E-5ECC-428A-9E0F-79AFBDFDC0A1}"/>
+    <hyperlink ref="C24" r:id="rId21" xr:uid="{E131E37A-2710-41A9-8E09-385A48A22B6E}"/>
+    <hyperlink ref="C25" r:id="rId22" xr:uid="{619AAEF6-A880-4FF2-A6A1-9AAED52AA7C3}"/>
+    <hyperlink ref="C26" r:id="rId23" xr:uid="{65B04FD4-E0D6-4862-8502-4BF8E1730BA5}"/>
+    <hyperlink ref="C27" r:id="rId24" xr:uid="{85DD1AA7-7AAF-433F-B7CD-6FC2603C7066}"/>
+    <hyperlink ref="C29" r:id="rId25" xr:uid="{023EBDAF-B529-4349-A162-0526693D85BA}"/>
+    <hyperlink ref="C50" r:id="rId26" xr:uid="{15B0E699-9A85-41E0-A7F3-EA5D264E39EC}"/>
+    <hyperlink ref="C75" r:id="rId27" display="https://static.wixstatic.com/media/f7d549_792ca485cfa042429d37c4a6ba3b2a29~mv2_d_3004_1496_s_2.png/v1/fill/w_185,h_80,al_c,q_85,usm_0.66_1.00_0.01,enc_avif,quality_auto/f7d549_792ca485cfa042429d37c4a6ba3b2a29~mv2_d_3004_1496_s_2.png" xr:uid="{FD1AA4EB-EDAD-4F60-8D99-29D1DDA7C967}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
